--- a/core/static/kozu_vor.xlsx
+++ b/core/static/kozu_vor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk-ushakov2.aa\YandexDisk\Удаленка\Общий диск\AMAST-автоматизация\amast_ta\core\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Artem\YandexDisk\Удаленка\Общий диск\AMAST-автоматизация\amast_ta\core\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0C9C72-C62E-4AF7-B17D-4EF22607E036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC2A9B9-3CF8-4A69-9EE3-3427086A8EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{8527E5F6-A312-4E33-AF0A-77ACF14CC2D0}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{8527E5F6-A312-4E33-AF0A-77ACF14CC2D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Исходные данные" sheetId="1" r:id="rId1"/>
@@ -1686,17 +1686,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C0149E-5743-4CBA-9DCF-CCA37AD3C7CF}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
@@ -1730,27 +1730,27 @@
       <c r="O1" s="45"/>
       <c r="P1" s="45"/>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>147</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="7">
-        <v>0.02</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1758,12 +1758,12 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="7">
-        <v>1.6E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1772,7 +1772,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>188</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1801,7 +1801,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>61</v>
       </c>
@@ -1813,7 +1813,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>31</v>
       </c>
@@ -1828,7 +1828,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
@@ -1840,13 +1840,13 @@
       </c>
       <c r="E9" s="1">
         <f>B5+(C3-2.5)*2</f>
-        <v>-4.9409999999999998</v>
+        <v>-4.9470000000000001</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>112</v>
       </c>
@@ -1855,12 +1855,12 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="7">
-        <v>15200</v>
+        <v>15.2</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
@@ -1874,10 +1874,10 @@
       </c>
       <c r="H11" s="5">
         <f>F10*0.0907</f>
-        <v>1378.64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
+        <v>1.3786400000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -1891,10 +1891,10 @@
       </c>
       <c r="H12" s="5">
         <f>F10*0.6082</f>
-        <v>9244.64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
+        <v>9.2446399999999986</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>63</v>
       </c>
@@ -1908,10 +1908,10 @@
       </c>
       <c r="H13" s="5">
         <f>F10*0.1207</f>
-        <v>1834.64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
+        <v>1.83464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>65</v>
       </c>
@@ -1925,10 +1925,10 @@
       </c>
       <c r="H14" s="5">
         <f>F10*0.1487</f>
-        <v>2260.2399999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
+        <v>2.26024</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>66</v>
       </c>
@@ -1942,10 +1942,10 @@
       </c>
       <c r="H15" s="5">
         <f>F10*0.0317</f>
-        <v>481.84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+        <v>0.48183999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>127</v>
       </c>
@@ -1953,7 +1953,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="4">
         <f>12796.03*H16</f>
-        <v>13673325.8168</v>
+        <v>13673.325816799999</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="3"/>
@@ -1962,10 +1962,10 @@
       </c>
       <c r="H16" s="5">
         <f>F10*0.0703</f>
-        <v>1068.56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1.06856</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>135</v>
       </c>
@@ -1980,7 +1980,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>138</v>
       </c>
@@ -1995,7 +1995,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>151</v>
       </c>
@@ -2009,7 +2009,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>154</v>
       </c>
@@ -2039,15 +2039,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G414"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="57.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="57.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="40.42578125" customWidth="1"/>
+    <col min="7" max="7" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2061,7 +2061,7 @@
       <c r="F1" s="47"/>
       <c r="G1" s="48"/>
     </row>
-    <row r="2" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="49" t="s">
         <v>190</v>
       </c>
@@ -2072,7 +2072,7 @@
       <c r="F2" s="50"/>
       <c r="G2" s="51"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
         <v>0</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="56"/>
       <c r="B4" s="58"/>
       <c r="C4" s="58"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G4" s="63"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>1</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="52" t="s">
         <v>1</v>
       </c>
@@ -2140,7 +2140,7 @@
       <c r="F6" s="53"/>
       <c r="G6" s="54"/>
     </row>
-    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <v>1</v>
       </c>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="D7" s="3">
         <f>(3.14*('Исходные данные'!B4/2+'Исходные данные'!B5/2)*'Исходные данные'!C3)*1.5/100</f>
-        <v>1.6485000000000002E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="E7" s="3">
         <f>D7*'Исходные данные'!D2</f>
-        <v>4.9455000000000007E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="F7" s="64" t="s">
         <v>33</v>
@@ -2165,7 +2165,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="16"/>
       <c r="B8" s="18" t="s">
         <v>87</v>
@@ -2176,7 +2176,7 @@
       <c r="F8" s="65"/>
       <c r="G8" s="68"/>
     </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="16"/>
       <c r="B9" s="19" t="s">
         <v>10</v>
@@ -2186,16 +2186,16 @@
       </c>
       <c r="D9" s="3">
         <f>0.009*D7</f>
-        <v>1.4836500000000002E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="E9" s="3">
         <f>D9*'Исходные данные'!D2</f>
-        <v>4.4509500000000006E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="F9" s="65"/>
       <c r="G9" s="68"/>
     </row>
-    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="19" t="s">
         <v>11</v>
@@ -2205,16 +2205,16 @@
       </c>
       <c r="D10" s="3">
         <f>0.035*D7</f>
-        <v>5.769750000000001E-7</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="E10" s="3">
         <f>D10*'Исходные данные'!D2</f>
-        <v>1.7309250000000003E-6</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="F10" s="65"/>
       <c r="G10" s="68"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
         <v>8</v>
@@ -2224,16 +2224,16 @@
       </c>
       <c r="D11" s="3">
         <f>3.4*D7</f>
-        <v>5.6049000000000005E-5</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="E11" s="3">
         <f>D11*'Исходные данные'!D2</f>
-        <v>1.68147E-4</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="F11" s="65"/>
       <c r="G11" s="68"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="18" t="s">
         <v>88</v>
@@ -2244,7 +2244,7 @@
       <c r="F12" s="65"/>
       <c r="G12" s="68"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
         <v>90</v>
@@ -2255,7 +2255,7 @@
       <c r="F13" s="66"/>
       <c r="G13" s="69"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="52" t="s">
         <v>172</v>
       </c>
@@ -2266,7 +2266,7 @@
       <c r="F14" s="53"/>
       <c r="G14" s="54"/>
     </row>
-    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <v>1</v>
       </c>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="E15" s="1">
         <f>D15*'Исходные данные'!D2</f>
-        <v>3.6000000000000004E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="F15" s="71" t="s">
         <v>177</v>
@@ -2291,7 +2291,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="18" t="s">
         <v>87</v>
@@ -2302,7 +2302,7 @@
       <c r="F16" s="71"/>
       <c r="G16" s="72"/>
     </row>
-    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="19" t="s">
         <v>175</v>
@@ -2315,12 +2315,12 @@
       </c>
       <c r="E17" s="1">
         <f>D17*'Исходные данные'!D2</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F17" s="71"/>
       <c r="G17" s="72"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="18" t="s">
         <v>88</v>
@@ -2331,7 +2331,7 @@
       <c r="F18" s="71"/>
       <c r="G18" s="72"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="19" t="s">
         <v>90</v>
@@ -2342,7 +2342,7 @@
       <c r="F19" s="71"/>
       <c r="G19" s="72"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="16">
         <v>2</v>
       </c>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E20" s="3">
         <f>D20*'Исходные данные'!D2</f>
-        <v>2.826E-2</v>
+        <v>9.4199999999999996E-3</v>
       </c>
       <c r="F20" s="71" t="s">
         <v>180</v>
@@ -2367,7 +2367,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="18" t="s">
         <v>87</v>
@@ -2378,7 +2378,7 @@
       <c r="F21" s="71"/>
       <c r="G21" s="72"/>
     </row>
-    <row r="22" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="19" t="s">
         <v>182</v>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="E22" s="1">
         <f>D22*'Исходные данные'!D2</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F22" s="71"/>
       <c r="G22" s="72"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="18" t="s">
         <v>88</v>
@@ -2407,7 +2407,7 @@
       <c r="F23" s="71"/>
       <c r="G23" s="72"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="17" t="s">
         <v>90</v>
@@ -2418,7 +2418,7 @@
       <c r="F24" s="71"/>
       <c r="G24" s="72"/>
     </row>
-    <row r="25" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16">
         <v>3</v>
       </c>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E25" s="3">
         <f>D25*'Исходные данные'!$D$2</f>
-        <v>4.2389999999999997E-2</v>
+        <v>1.4129999999999998E-2</v>
       </c>
       <c r="F25" s="73"/>
       <c r="G25" s="67"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="18" t="s">
         <v>87</v>
@@ -2450,7 +2450,7 @@
       <c r="F26" s="74"/>
       <c r="G26" s="68"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="19" t="s">
         <v>16</v>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="E27" s="3">
         <f>E25</f>
-        <v>4.2389999999999997E-2</v>
+        <v>1.4129999999999998E-2</v>
       </c>
       <c r="F27" s="74"/>
       <c r="G27" s="68"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="18" t="s">
         <v>88</v>
@@ -2480,7 +2480,7 @@
       <c r="F28" s="74"/>
       <c r="G28" s="68"/>
     </row>
-    <row r="29" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="19" t="s">
         <v>113</v>
@@ -2491,7 +2491,7 @@
       <c r="F29" s="74"/>
       <c r="G29" s="68"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="21" t="s">
         <v>144</v>
@@ -2502,7 +2502,7 @@
       <c r="F30" s="74"/>
       <c r="G30" s="68"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="17" t="s">
         <v>90</v>
@@ -2513,7 +2513,7 @@
       <c r="F31" s="74"/>
       <c r="G31" s="68"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="17" t="s">
         <v>134</v>
@@ -2524,7 +2524,7 @@
       <c r="F32" s="75"/>
       <c r="G32" s="69"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="52" t="s">
         <v>62</v>
       </c>
@@ -2535,7 +2535,7 @@
       <c r="F33" s="53"/>
       <c r="G33" s="54"/>
     </row>
-    <row r="34" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16">
         <v>1</v>
       </c>
@@ -2547,18 +2547,18 @@
       </c>
       <c r="D34" s="3">
         <f>'Исходные данные'!H11</f>
-        <v>1378.64</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="E34" s="3">
         <f>D34*'Исходные данные'!$D$2</f>
-        <v>4135.92</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="F34" s="64" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="67"/>
     </row>
-    <row r="35" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="18" t="s">
         <v>87</v>
@@ -2569,7 +2569,7 @@
       <c r="F35" s="65"/>
       <c r="G35" s="68"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="19" t="s">
         <v>16</v>
@@ -2579,16 +2579,16 @@
       </c>
       <c r="D36" s="3">
         <f>D34</f>
-        <v>1378.64</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="E36" s="3">
         <f>D36*'Исходные данные'!$D$2</f>
-        <v>4135.92</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="F36" s="65"/>
       <c r="G36" s="68"/>
     </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="18" t="s">
         <v>88</v>
@@ -2599,7 +2599,7 @@
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
     </row>
-    <row r="38" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="19" t="s">
         <v>113</v>
@@ -2610,7 +2610,7 @@
       <c r="F38" s="65"/>
       <c r="G38" s="68"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="21" t="s">
         <v>144</v>
@@ -2621,7 +2621,7 @@
       <c r="F39" s="65"/>
       <c r="G39" s="68"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="17" t="s">
         <v>90</v>
@@ -2632,7 +2632,7 @@
       <c r="F40" s="65"/>
       <c r="G40" s="68"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="17" t="s">
         <v>134</v>
@@ -2643,7 +2643,7 @@
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
     </row>
-    <row r="42" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="16">
         <v>2</v>
       </c>
@@ -2655,16 +2655,16 @@
       </c>
       <c r="D42" s="3">
         <f>'Исходные данные'!H12</f>
-        <v>9244.64</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="E42" s="3">
         <f>D42*'Исходные данные'!$D$2</f>
-        <v>27733.919999999998</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="F42" s="65"/>
       <c r="G42" s="68"/>
     </row>
-    <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="18" t="s">
         <v>87</v>
@@ -2675,7 +2675,7 @@
       <c r="F43" s="65"/>
       <c r="G43" s="68"/>
     </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="19" t="s">
         <v>16</v>
@@ -2685,16 +2685,16 @@
       </c>
       <c r="D44" s="3">
         <f>D42</f>
-        <v>9244.64</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="E44" s="3">
         <f>D44*'Исходные данные'!$D$2</f>
-        <v>27733.919999999998</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="F44" s="65"/>
       <c r="G44" s="68"/>
     </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="18" t="s">
         <v>88</v>
@@ -2705,7 +2705,7 @@
       <c r="F45" s="65"/>
       <c r="G45" s="68"/>
     </row>
-    <row r="46" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="19" t="s">
         <v>113</v>
@@ -2716,7 +2716,7 @@
       <c r="F46" s="65"/>
       <c r="G46" s="68"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="19" t="s">
         <v>144</v>
@@ -2727,7 +2727,7 @@
       <c r="F47" s="65"/>
       <c r="G47" s="68"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="17" t="s">
         <v>90</v>
@@ -2738,7 +2738,7 @@
       <c r="F48" s="65"/>
       <c r="G48" s="68"/>
     </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="17" t="s">
         <v>134</v>
@@ -2749,7 +2749,7 @@
       <c r="F49" s="65"/>
       <c r="G49" s="68"/>
     </row>
-    <row r="50" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A50" s="16">
         <v>3</v>
       </c>
@@ -2761,16 +2761,16 @@
       </c>
       <c r="D50" s="3">
         <f>'Исходные данные'!H13</f>
-        <v>1834.64</v>
+        <v>1.83464</v>
       </c>
       <c r="E50" s="3">
         <f>D50*'Исходные данные'!$D$2</f>
-        <v>5503.92</v>
+        <v>1.83464</v>
       </c>
       <c r="F50" s="65"/>
       <c r="G50" s="68"/>
     </row>
-    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="18" t="s">
         <v>87</v>
@@ -2781,7 +2781,7 @@
       <c r="F51" s="65"/>
       <c r="G51" s="68"/>
     </row>
-    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="19" t="s">
         <v>16</v>
@@ -2791,16 +2791,16 @@
       </c>
       <c r="D52" s="3">
         <f>D50</f>
-        <v>1834.64</v>
+        <v>1.83464</v>
       </c>
       <c r="E52" s="3">
         <f>D52*'Исходные данные'!$D$2</f>
-        <v>5503.92</v>
+        <v>1.83464</v>
       </c>
       <c r="F52" s="65"/>
       <c r="G52" s="68"/>
     </row>
-    <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="18" t="s">
         <v>88</v>
@@ -2811,7 +2811,7 @@
       <c r="F53" s="65"/>
       <c r="G53" s="68"/>
     </row>
-    <row r="54" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="19" t="s">
         <v>113</v>
@@ -2822,7 +2822,7 @@
       <c r="F54" s="65"/>
       <c r="G54" s="68"/>
     </row>
-    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="19" t="s">
         <v>144</v>
@@ -2833,7 +2833,7 @@
       <c r="F55" s="65"/>
       <c r="G55" s="68"/>
     </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="17" t="s">
         <v>90</v>
@@ -2844,7 +2844,7 @@
       <c r="F56" s="65"/>
       <c r="G56" s="68"/>
     </row>
-    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="17" t="s">
         <v>134</v>
@@ -2855,7 +2855,7 @@
       <c r="F57" s="65"/>
       <c r="G57" s="68"/>
     </row>
-    <row r="58" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="16">
         <v>4</v>
       </c>
@@ -2867,16 +2867,16 @@
       </c>
       <c r="D58" s="3">
         <f>'Исходные данные'!H14</f>
-        <v>2260.2399999999998</v>
+        <v>2.26024</v>
       </c>
       <c r="E58" s="3">
         <f>D58*'Исходные данные'!$D$2</f>
-        <v>6780.7199999999993</v>
+        <v>2.26024</v>
       </c>
       <c r="F58" s="65"/>
       <c r="G58" s="68"/>
     </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="18" t="s">
         <v>87</v>
@@ -2887,7 +2887,7 @@
       <c r="F59" s="65"/>
       <c r="G59" s="68"/>
     </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="19" t="s">
         <v>16</v>
@@ -2897,16 +2897,16 @@
       </c>
       <c r="D60" s="3">
         <f>D58</f>
-        <v>2260.2399999999998</v>
+        <v>2.26024</v>
       </c>
       <c r="E60" s="3">
         <f>D60*'Исходные данные'!$D$2</f>
-        <v>6780.7199999999993</v>
+        <v>2.26024</v>
       </c>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
     </row>
-    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="18" t="s">
         <v>88</v>
@@ -2917,7 +2917,7 @@
       <c r="F61" s="65"/>
       <c r="G61" s="68"/>
     </row>
-    <row r="62" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="19" t="s">
         <v>113</v>
@@ -2928,7 +2928,7 @@
       <c r="F62" s="65"/>
       <c r="G62" s="68"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="19" t="s">
         <v>144</v>
@@ -2939,7 +2939,7 @@
       <c r="F63" s="65"/>
       <c r="G63" s="68"/>
     </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="17" t="s">
         <v>90</v>
@@ -2950,7 +2950,7 @@
       <c r="F64" s="65"/>
       <c r="G64" s="68"/>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="17" t="s">
         <v>134</v>
@@ -2961,7 +2961,7 @@
       <c r="F65" s="65"/>
       <c r="G65" s="68"/>
     </row>
-    <row r="66" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A66" s="16">
         <v>5</v>
       </c>
@@ -2973,16 +2973,16 @@
       </c>
       <c r="D66" s="3">
         <f>'Исходные данные'!H15</f>
-        <v>481.84</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="E66" s="3">
         <f>D66*'Исходные данные'!$D$2</f>
-        <v>1445.52</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="F66" s="65"/>
       <c r="G66" s="68"/>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="18" t="s">
         <v>87</v>
@@ -2993,7 +2993,7 @@
       <c r="F67" s="65"/>
       <c r="G67" s="68"/>
     </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="19" t="s">
         <v>16</v>
@@ -3003,16 +3003,16 @@
       </c>
       <c r="D68" s="3">
         <f>D66</f>
-        <v>481.84</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="E68" s="3">
         <f>D68*'Исходные данные'!$D$2</f>
-        <v>1445.52</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="F68" s="65"/>
       <c r="G68" s="68"/>
     </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="18" t="s">
         <v>88</v>
@@ -3023,7 +3023,7 @@
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
     </row>
-    <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="19" t="s">
         <v>113</v>
@@ -3034,7 +3034,7 @@
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="19" t="s">
         <v>144</v>
@@ -3045,7 +3045,7 @@
       <c r="F71" s="65"/>
       <c r="G71" s="68"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="17" t="s">
         <v>90</v>
@@ -3056,7 +3056,7 @@
       <c r="F72" s="65"/>
       <c r="G72" s="68"/>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="17" t="s">
         <v>134</v>
@@ -3067,7 +3067,7 @@
       <c r="F73" s="66"/>
       <c r="G73" s="69"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="16">
         <v>6</v>
       </c>
@@ -3079,11 +3079,11 @@
       </c>
       <c r="D74" s="3">
         <f>'Исходные данные'!D16/100</f>
-        <v>136733.258168</v>
+        <v>136.73325816799999</v>
       </c>
       <c r="E74" s="3">
         <f>D74*'Исходные данные'!$D$2</f>
-        <v>410199.77450399997</v>
+        <v>136.73325816799999</v>
       </c>
       <c r="F74" s="64" t="s">
         <v>19</v>
@@ -3092,7 +3092,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="18" t="s">
         <v>87</v>
@@ -3103,7 +3103,7 @@
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="19" t="s">
         <v>126</v>
@@ -3113,16 +3113,16 @@
       </c>
       <c r="D76" s="3">
         <f>'Исходные данные'!H16</f>
-        <v>1068.56</v>
+        <v>1.06856</v>
       </c>
       <c r="E76" s="3">
         <f>D76*'Исходные данные'!$D$2</f>
-        <v>3205.68</v>
+        <v>1.06856</v>
       </c>
       <c r="F76" s="65"/>
       <c r="G76" s="68"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="18" t="s">
         <v>88</v>
@@ -3133,7 +3133,7 @@
       <c r="F77" s="65"/>
       <c r="G77" s="68"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
       <c r="B78" s="19" t="s">
         <v>90</v>
@@ -3144,7 +3144,7 @@
       <c r="F78" s="66"/>
       <c r="G78" s="69"/>
     </row>
-    <row r="79" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A79" s="70" t="s">
         <v>28</v>
       </c>
@@ -3154,16 +3154,16 @@
       </c>
       <c r="D79" s="3">
         <f>D34+D42+D50+D58+D66</f>
-        <v>15199.999999999998</v>
+        <v>15.2</v>
       </c>
       <c r="E79" s="3">
         <f>D79*'Исходные данные'!$D$2</f>
-        <v>45599.999999999993</v>
+        <v>15.2</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="20"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="70" t="s">
         <v>128</v>
       </c>
@@ -3173,16 +3173,16 @@
       </c>
       <c r="D80" s="3">
         <f>D76</f>
-        <v>1068.56</v>
+        <v>1.06856</v>
       </c>
       <c r="E80" s="3">
         <f>D80*'Исходные данные'!$D$2</f>
-        <v>3205.68</v>
+        <v>1.06856</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="20"/>
     </row>
-    <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="70" t="s">
         <v>129</v>
       </c>
@@ -3192,16 +3192,16 @@
       </c>
       <c r="D81" s="3">
         <f>D79+D80</f>
-        <v>16268.559999999998</v>
+        <v>16.268560000000001</v>
       </c>
       <c r="E81" s="3">
         <f>D81*'Исходные данные'!$D$2</f>
-        <v>48805.679999999993</v>
+        <v>16.268560000000001</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="20"/>
     </row>
-    <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="52" t="s">
         <v>184</v>
       </c>
@@ -3212,7 +3212,7 @@
       <c r="F82" s="53"/>
       <c r="G82" s="54"/>
     </row>
-    <row r="83" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A83" s="16">
         <v>1</v>
       </c>
@@ -3228,14 +3228,14 @@
       </c>
       <c r="E83" s="3">
         <f>D83*'Исходные данные'!$D$2</f>
-        <v>-3.78E-2</v>
+        <v>-1.26E-2</v>
       </c>
       <c r="F83" s="64" t="s">
         <v>19</v>
       </c>
       <c r="G83" s="67"/>
     </row>
-    <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="16"/>
       <c r="B84" s="18" t="s">
         <v>87</v>
@@ -3246,7 +3246,7 @@
       <c r="F84" s="65"/>
       <c r="G84" s="68"/>
     </row>
-    <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="16"/>
       <c r="B85" s="19" t="s">
         <v>16</v>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="E85" s="3">
         <f>D85*'Исходные данные'!$D$2</f>
-        <v>-3.78E-2</v>
+        <v>-1.26E-2</v>
       </c>
       <c r="F85" s="65"/>
       <c r="G85" s="68"/>
     </row>
-    <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="16"/>
       <c r="B86" s="18" t="s">
         <v>88</v>
@@ -3276,7 +3276,7 @@
       <c r="F86" s="65"/>
       <c r="G86" s="68"/>
     </row>
-    <row r="87" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A87" s="16"/>
       <c r="B87" s="19" t="s">
         <v>113</v>
@@ -3287,7 +3287,7 @@
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
     </row>
-    <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="16"/>
       <c r="B88" s="19" t="s">
         <v>144</v>
@@ -3298,7 +3298,7 @@
       <c r="F88" s="65"/>
       <c r="G88" s="68"/>
     </row>
-    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="16"/>
       <c r="B89" s="17" t="s">
         <v>90</v>
@@ -3309,7 +3309,7 @@
       <c r="F89" s="65"/>
       <c r="G89" s="68"/>
     </row>
-    <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="16"/>
       <c r="B90" s="17" t="s">
         <v>134</v>
@@ -3320,7 +3320,7 @@
       <c r="F90" s="66"/>
       <c r="G90" s="69"/>
     </row>
-    <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="16">
         <v>2</v>
       </c>
@@ -3336,12 +3336,12 @@
       </c>
       <c r="E91" s="1">
         <f>D91*'Исходные данные'!$D$2</f>
-        <v>-90</v>
+        <v>-30</v>
       </c>
       <c r="F91" s="73"/>
       <c r="G91" s="67"/>
     </row>
-    <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="16"/>
       <c r="B92" s="18" t="s">
         <v>87</v>
@@ -3352,7 +3352,7 @@
       <c r="F92" s="74"/>
       <c r="G92" s="68"/>
     </row>
-    <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="16"/>
       <c r="B93" s="17" t="s">
         <v>35</v>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E93" s="4">
         <f>D93*'Исходные данные'!$D$2</f>
-        <v>-90</v>
+        <v>-30</v>
       </c>
       <c r="F93" s="74"/>
       <c r="G93" s="68"/>
     </row>
-    <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="16"/>
       <c r="B94" s="18" t="s">
         <v>88</v>
@@ -3382,7 +3382,7 @@
       <c r="F94" s="74"/>
       <c r="G94" s="68"/>
     </row>
-    <row r="95" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A95" s="16"/>
       <c r="B95" s="19" t="s">
         <v>113</v>
@@ -3393,7 +3393,7 @@
       <c r="F95" s="74"/>
       <c r="G95" s="68"/>
     </row>
-    <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="16"/>
       <c r="B96" s="19" t="s">
         <v>144</v>
@@ -3404,7 +3404,7 @@
       <c r="F96" s="74"/>
       <c r="G96" s="68"/>
     </row>
-    <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="16"/>
       <c r="B97" s="17" t="s">
         <v>90</v>
@@ -3415,7 +3415,7 @@
       <c r="F97" s="74"/>
       <c r="G97" s="68"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="16"/>
       <c r="B98" s="17" t="s">
         <v>134</v>
@@ -3426,7 +3426,7 @@
       <c r="F98" s="75"/>
       <c r="G98" s="69"/>
     </row>
-    <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="16">
         <v>3</v>
       </c>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="E99" s="4">
         <f>D99*'Исходные данные'!$D$2</f>
-        <v>-5.3693999999999999E-3</v>
+        <v>-1.7898E-3</v>
       </c>
       <c r="F99" s="64"/>
       <c r="G99" s="67"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="16"/>
       <c r="B100" s="18" t="s">
         <v>87</v>
@@ -3458,7 +3458,7 @@
       <c r="F100" s="65"/>
       <c r="G100" s="68"/>
     </row>
-    <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="16"/>
       <c r="B101" s="1" t="s">
         <v>74</v>
@@ -3472,12 +3472,12 @@
       </c>
       <c r="E101" s="1">
         <f>D101*'Исходные данные'!$D$2</f>
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="F101" s="65"/>
       <c r="G101" s="68"/>
     </row>
-    <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="16"/>
       <c r="B102" s="18" t="s">
         <v>88</v>
@@ -3488,7 +3488,7 @@
       <c r="F102" s="65"/>
       <c r="G102" s="68"/>
     </row>
-    <row r="103" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A103" s="16"/>
       <c r="B103" s="19" t="s">
         <v>113</v>
@@ -3499,7 +3499,7 @@
       <c r="F103" s="65"/>
       <c r="G103" s="68"/>
     </row>
-    <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="16"/>
       <c r="B104" s="19" t="s">
         <v>144</v>
@@ -3510,7 +3510,7 @@
       <c r="F104" s="65"/>
       <c r="G104" s="68"/>
     </row>
-    <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="16"/>
       <c r="B105" s="17" t="s">
         <v>90</v>
@@ -3521,7 +3521,7 @@
       <c r="F105" s="65"/>
       <c r="G105" s="68"/>
     </row>
-    <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="16"/>
       <c r="B106" s="17" t="s">
         <v>134</v>
@@ -3532,7 +3532,7 @@
       <c r="F106" s="66"/>
       <c r="G106" s="69"/>
     </row>
-    <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="16">
         <v>4</v>
       </c>
@@ -3544,16 +3544,16 @@
       </c>
       <c r="D107" s="4">
         <f>('Исходные данные'!D9*('Исходные данные'!B5+2*'Исходные данные'!C3-2.5+0.4))/100</f>
-        <v>0.30614999999999998</v>
+        <v>0.30705000000000005</v>
       </c>
       <c r="E107" s="4">
         <f>D107*'Исходные данные'!$D$2</f>
-        <v>0.91844999999999999</v>
+        <v>0.30705000000000005</v>
       </c>
       <c r="F107" s="64"/>
       <c r="G107" s="67"/>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="16"/>
       <c r="B108" s="18" t="s">
         <v>87</v>
@@ -3564,7 +3564,7 @@
       <c r="F108" s="65"/>
       <c r="G108" s="68"/>
     </row>
-    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="16"/>
       <c r="B109" s="1" t="s">
         <v>74</v>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E109" s="1">
         <f>D109*'Исходные данные'!$D$2</f>
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="F109" s="65"/>
       <c r="G109" s="68"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="16"/>
       <c r="B110" s="18" t="s">
         <v>88</v>
@@ -3594,7 +3594,7 @@
       <c r="F110" s="65"/>
       <c r="G110" s="68"/>
     </row>
-    <row r="111" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A111" s="16"/>
       <c r="B111" s="19" t="s">
         <v>113</v>
@@ -3605,7 +3605,7 @@
       <c r="F111" s="65"/>
       <c r="G111" s="68"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="16"/>
       <c r="B112" s="19" t="s">
         <v>144</v>
@@ -3616,7 +3616,7 @@
       <c r="F112" s="65"/>
       <c r="G112" s="68"/>
     </row>
-    <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="16"/>
       <c r="B113" s="17" t="s">
         <v>90</v>
@@ -3627,7 +3627,7 @@
       <c r="F113" s="65"/>
       <c r="G113" s="68"/>
     </row>
-    <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="16"/>
       <c r="B114" s="17" t="s">
         <v>134</v>
@@ -3638,7 +3638,7 @@
       <c r="F114" s="66"/>
       <c r="G114" s="69"/>
     </row>
-    <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="16">
         <v>5</v>
       </c>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="E115" s="1">
         <f>D115*'Исходные данные'!$D$2</f>
-        <v>-57</v>
+        <v>-19</v>
       </c>
       <c r="F115" s="76"/>
       <c r="G115" s="72"/>
     </row>
-    <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="16"/>
       <c r="B116" s="18" t="s">
         <v>87</v>
@@ -3670,7 +3670,7 @@
       <c r="F116" s="76"/>
       <c r="G116" s="72"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="16"/>
       <c r="B117" s="17" t="s">
         <v>38</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E117" s="1">
         <f>D117*'Исходные данные'!$D$2</f>
-        <v>-57</v>
+        <v>-19</v>
       </c>
       <c r="F117" s="76"/>
       <c r="G117" s="72"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="16"/>
       <c r="B118" s="18" t="s">
         <v>88</v>
@@ -3700,7 +3700,7 @@
       <c r="F118" s="76"/>
       <c r="G118" s="72"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="16"/>
       <c r="B119" s="19" t="s">
         <v>113</v>
@@ -3711,7 +3711,7 @@
       <c r="F119" s="76"/>
       <c r="G119" s="72"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="16"/>
       <c r="B120" s="19" t="s">
         <v>144</v>
@@ -3722,7 +3722,7 @@
       <c r="F120" s="76"/>
       <c r="G120" s="72"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="16"/>
       <c r="B121" s="17" t="s">
         <v>90</v>
@@ -3733,7 +3733,7 @@
       <c r="F121" s="76"/>
       <c r="G121" s="72"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="16"/>
       <c r="B122" s="17" t="s">
         <v>134</v>
@@ -3744,7 +3744,7 @@
       <c r="F122" s="76"/>
       <c r="G122" s="72"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="52" t="s">
         <v>185</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="F123" s="53"/>
       <c r="G123" s="54"/>
     </row>
-    <row r="124" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="16">
         <v>1</v>
       </c>
@@ -3771,14 +3771,14 @@
       </c>
       <c r="E124" s="1">
         <f>D124*'Исходные данные'!$D$2</f>
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F124" s="64" t="s">
         <v>19</v>
       </c>
       <c r="G124" s="67"/>
     </row>
-    <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="16"/>
       <c r="B125" s="18" t="s">
         <v>87</v>
@@ -3789,7 +3789,7 @@
       <c r="F125" s="65"/>
       <c r="G125" s="68"/>
     </row>
-    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="16"/>
       <c r="B126" s="19" t="s">
         <v>16</v>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E126" s="1">
         <f>D126*'Исходные данные'!$D$2</f>
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F126" s="65"/>
       <c r="G126" s="68"/>
     </row>
-    <row r="127" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="16"/>
       <c r="B127" s="18" t="s">
         <v>88</v>
@@ -3819,7 +3819,7 @@
       <c r="F127" s="65"/>
       <c r="G127" s="68"/>
     </row>
-    <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="16"/>
       <c r="B128" s="19" t="s">
         <v>113</v>
@@ -3830,7 +3830,7 @@
       <c r="F128" s="65"/>
       <c r="G128" s="68"/>
     </row>
-    <row r="129" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="16"/>
       <c r="B129" s="17" t="s">
         <v>90</v>
@@ -3841,7 +3841,7 @@
       <c r="F129" s="65"/>
       <c r="G129" s="68"/>
     </row>
-    <row r="130" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="16"/>
       <c r="B130" s="17" t="s">
         <v>134</v>
@@ -3852,7 +3852,7 @@
       <c r="F130" s="66"/>
       <c r="G130" s="69"/>
     </row>
-    <row r="131" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="16">
         <v>2</v>
       </c>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="E131" s="1">
         <f>D131*'Исходные данные'!$D$2</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F131" s="64"/>
       <c r="G131" s="67"/>
     </row>
-    <row r="132" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="16"/>
       <c r="B132" s="18" t="s">
         <v>87</v>
@@ -3883,7 +3883,7 @@
       <c r="F132" s="65"/>
       <c r="G132" s="68"/>
     </row>
-    <row r="133" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="16"/>
       <c r="B133" s="17" t="s">
         <v>136</v>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="E133" s="1">
         <f>D133*'Исходные данные'!$D$2</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F133" s="66"/>
       <c r="G133" s="69"/>
     </row>
-    <row r="134" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="16">
         <v>3</v>
       </c>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E134" s="1">
         <f>D134*'Исходные данные'!$D$2</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F134" s="64"/>
       <c r="G134" s="67"/>
     </row>
-    <row r="135" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="16"/>
       <c r="B135" s="18" t="s">
         <v>87</v>
@@ -3932,7 +3932,7 @@
       <c r="F135" s="65"/>
       <c r="G135" s="68"/>
     </row>
-    <row r="136" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="16"/>
       <c r="B136" s="17" t="s">
         <v>39</v>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="E136" s="1">
         <f>D136*'Исходные данные'!$D$2</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F136" s="66"/>
       <c r="G136" s="69"/>
     </row>
-    <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="52" t="s">
         <v>186</v>
       </c>
@@ -3961,7 +3961,7 @@
       <c r="F137" s="53"/>
       <c r="G137" s="54"/>
     </row>
-    <row r="138" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A138" s="16">
         <v>1</v>
       </c>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="G138" s="67"/>
     </row>
-    <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="16"/>
       <c r="B139" s="18" t="s">
         <v>87</v>
@@ -3995,7 +3995,7 @@
       <c r="F139" s="65"/>
       <c r="G139" s="68"/>
     </row>
-    <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="16"/>
       <c r="B140" s="2" t="s">
         <v>16</v>
@@ -4014,7 +4014,7 @@
       <c r="F140" s="65"/>
       <c r="G140" s="68"/>
     </row>
-    <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="16"/>
       <c r="B141" s="18" t="s">
         <v>88</v>
@@ -4025,7 +4025,7 @@
       <c r="F141" s="65"/>
       <c r="G141" s="68"/>
     </row>
-    <row r="142" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A142" s="16"/>
       <c r="B142" s="19" t="s">
         <v>113</v>
@@ -4036,7 +4036,7 @@
       <c r="F142" s="65"/>
       <c r="G142" s="68"/>
     </row>
-    <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="16"/>
       <c r="B143" s="19" t="s">
         <v>144</v>
@@ -4047,7 +4047,7 @@
       <c r="F143" s="65"/>
       <c r="G143" s="68"/>
     </row>
-    <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="16"/>
       <c r="B144" s="17" t="s">
         <v>90</v>
@@ -4058,7 +4058,7 @@
       <c r="F144" s="65"/>
       <c r="G144" s="68"/>
     </row>
-    <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="16"/>
       <c r="B145" s="17" t="s">
         <v>134</v>
@@ -4069,7 +4069,7 @@
       <c r="F145" s="66"/>
       <c r="G145" s="69"/>
     </row>
-    <row r="146" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="16">
         <v>2</v>
       </c>
@@ -4085,14 +4085,14 @@
       </c>
       <c r="E146" s="3">
         <f>D146*'Исходные данные'!$D$2</f>
-        <v>2.9209800000000001E-2</v>
+        <v>9.7365999999999998E-3</v>
       </c>
       <c r="F146" s="64"/>
       <c r="G146" s="67" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="16"/>
       <c r="B147" s="18" t="s">
         <v>87</v>
@@ -4103,7 +4103,7 @@
       <c r="F147" s="65"/>
       <c r="G147" s="68"/>
     </row>
-    <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="16"/>
       <c r="B148" s="19" t="s">
         <v>75</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="E148" s="4">
         <f>D148*'Исходные данные'!$D$2</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="65"/>
       <c r="G148" s="68"/>
     </row>
-    <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="16"/>
       <c r="B149" s="18" t="s">
         <v>88</v>
@@ -4132,7 +4132,7 @@
       <c r="F149" s="65"/>
       <c r="G149" s="68"/>
     </row>
-    <row r="150" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A150" s="16"/>
       <c r="B150" s="19" t="s">
         <v>141</v>
@@ -4143,7 +4143,7 @@
       <c r="F150" s="65"/>
       <c r="G150" s="68"/>
     </row>
-    <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="16"/>
       <c r="B151" s="19" t="s">
         <v>142</v>
@@ -4154,7 +4154,7 @@
       <c r="F151" s="65"/>
       <c r="G151" s="68"/>
     </row>
-    <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="16"/>
       <c r="B152" s="19" t="s">
         <v>90</v>
@@ -4165,7 +4165,7 @@
       <c r="F152" s="66"/>
       <c r="G152" s="69"/>
     </row>
-    <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="16">
         <v>3</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="F153" s="64"/>
       <c r="G153" s="67"/>
     </row>
-    <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="16"/>
       <c r="B154" s="18" t="s">
         <v>87</v>
@@ -4197,7 +4197,7 @@
       <c r="F154" s="65"/>
       <c r="G154" s="68"/>
     </row>
-    <row r="155" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A155" s="16"/>
       <c r="B155" s="19" t="s">
         <v>139</v>
@@ -4216,7 +4216,7 @@
       <c r="F155" s="65"/>
       <c r="G155" s="68"/>
     </row>
-    <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="16"/>
       <c r="B156" s="18" t="s">
         <v>88</v>
@@ -4227,7 +4227,7 @@
       <c r="F156" s="65"/>
       <c r="G156" s="68"/>
     </row>
-    <row r="157" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A157" s="16"/>
       <c r="B157" s="19" t="s">
         <v>113</v>
@@ -4238,7 +4238,7 @@
       <c r="F157" s="65"/>
       <c r="G157" s="68"/>
     </row>
-    <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="16"/>
       <c r="B158" s="19" t="s">
         <v>144</v>
@@ -4249,7 +4249,7 @@
       <c r="F158" s="65"/>
       <c r="G158" s="68"/>
     </row>
-    <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="16"/>
       <c r="B159" s="17" t="s">
         <v>90</v>
@@ -4260,7 +4260,7 @@
       <c r="F159" s="65"/>
       <c r="G159" s="68"/>
     </row>
-    <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="16"/>
       <c r="B160" s="17" t="s">
         <v>134</v>
@@ -4271,7 +4271,7 @@
       <c r="F160" s="66"/>
       <c r="G160" s="69"/>
     </row>
-    <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="16">
         <v>4</v>
       </c>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="E161" s="3">
         <f>D161*'Исходные данные'!$D$2</f>
-        <v>8.5015500000000001E-4</v>
+        <v>2.8338499999999998E-4</v>
       </c>
       <c r="F161" s="64"/>
       <c r="G161" s="67" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="16"/>
       <c r="B162" s="18" t="s">
         <v>87</v>
@@ -4305,7 +4305,7 @@
       <c r="F162" s="65"/>
       <c r="G162" s="68"/>
     </row>
-    <row r="163" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A163" s="16"/>
       <c r="B163" s="19" t="s">
         <v>25</v>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="E163" s="3">
         <f>D163*'Исходные данные'!$D$2</f>
-        <v>8.5015499999999995E-7</v>
+        <v>2.8338499999999997E-7</v>
       </c>
       <c r="F163" s="65"/>
       <c r="G163" s="68"/>
     </row>
-    <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="16"/>
       <c r="B164" s="18" t="s">
         <v>88</v>
@@ -4335,7 +4335,7 @@
       <c r="F164" s="65"/>
       <c r="G164" s="68"/>
     </row>
-    <row r="165" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A165" s="16"/>
       <c r="B165" s="19" t="s">
         <v>113</v>
@@ -4346,7 +4346,7 @@
       <c r="F165" s="65"/>
       <c r="G165" s="68"/>
     </row>
-    <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="16"/>
       <c r="B166" s="17" t="s">
         <v>90</v>
@@ -4357,7 +4357,7 @@
       <c r="F166" s="65"/>
       <c r="G166" s="68"/>
     </row>
-    <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="16"/>
       <c r="B167" s="17" t="s">
         <v>134</v>
@@ -4368,7 +4368,7 @@
       <c r="F167" s="66"/>
       <c r="G167" s="69"/>
     </row>
-    <row r="168" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="52" t="s">
         <v>187</v>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="F168" s="53"/>
       <c r="G168" s="54"/>
     </row>
-    <row r="169" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="16">
         <v>1</v>
       </c>
@@ -4392,11 +4392,11 @@
       </c>
       <c r="D169" s="3">
         <f>D7</f>
-        <v>1.6485000000000002E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="E169" s="3">
         <f>D169*'Исходные данные'!$D$2</f>
-        <v>4.9455000000000007E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="F169" s="64" t="s">
         <v>33</v>
@@ -4405,7 +4405,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="16"/>
       <c r="B170" s="18" t="s">
         <v>87</v>
@@ -4416,7 +4416,7 @@
       <c r="F170" s="65"/>
       <c r="G170" s="68"/>
     </row>
-    <row r="171" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A171" s="16"/>
       <c r="B171" s="19" t="str">
         <f>B9</f>
@@ -4428,16 +4428,16 @@
       </c>
       <c r="D171" s="3">
         <f>D9</f>
-        <v>1.4836500000000002E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="E171" s="3">
         <f>D171*'Исходные данные'!$D$2</f>
-        <v>4.4509500000000006E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="F171" s="65"/>
       <c r="G171" s="68"/>
     </row>
-    <row r="172" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A172" s="16"/>
       <c r="B172" s="19" t="str">
         <f t="shared" ref="B172:D173" si="0">B10</f>
@@ -4449,16 +4449,16 @@
       </c>
       <c r="D172" s="3">
         <f t="shared" si="0"/>
-        <v>5.769750000000001E-7</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="E172" s="3">
         <f>D172*'Исходные данные'!$D$2</f>
-        <v>1.7309250000000003E-6</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="F172" s="65"/>
       <c r="G172" s="68"/>
     </row>
-    <row r="173" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="16"/>
       <c r="B173" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4470,16 +4470,16 @@
       </c>
       <c r="D173" s="3">
         <f t="shared" si="0"/>
-        <v>5.6049000000000005E-5</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="E173" s="3">
         <f>D173*'Исходные данные'!$D$2</f>
-        <v>1.68147E-4</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="F173" s="65"/>
       <c r="G173" s="68"/>
     </row>
-    <row r="174" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="16"/>
       <c r="B174" s="18" t="s">
         <v>88</v>
@@ -4490,7 +4490,7 @@
       <c r="F174" s="65"/>
       <c r="G174" s="68"/>
     </row>
-    <row r="175" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="16"/>
       <c r="B175" s="17" t="s">
         <v>90</v>
@@ -4501,7 +4501,7 @@
       <c r="F175" s="66"/>
       <c r="G175" s="69"/>
     </row>
-    <row r="176" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="52" t="s">
         <v>60</v>
       </c>
@@ -4512,7 +4512,7 @@
       <c r="F176" s="53"/>
       <c r="G176" s="54"/>
     </row>
-    <row r="177" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A177" s="16">
         <v>1</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="16"/>
       <c r="B178" s="18" t="s">
         <v>87</v>
@@ -4543,7 +4543,7 @@
       <c r="F178" s="65"/>
       <c r="G178" s="68"/>
     </row>
-    <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="16"/>
       <c r="B179" s="19" t="s">
         <v>16</v>
@@ -4559,7 +4559,7 @@
       <c r="F179" s="65"/>
       <c r="G179" s="68"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="16"/>
       <c r="B180" s="19" t="s">
         <v>150</v>
@@ -4575,7 +4575,7 @@
       <c r="F180" s="65"/>
       <c r="G180" s="68"/>
     </row>
-    <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="16"/>
       <c r="B181" s="18" t="s">
         <v>88</v>
@@ -4586,7 +4586,7 @@
       <c r="F181" s="65"/>
       <c r="G181" s="68"/>
     </row>
-    <row r="182" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A182" s="16"/>
       <c r="B182" s="19" t="s">
         <v>152</v>
@@ -4597,7 +4597,7 @@
       <c r="F182" s="65"/>
       <c r="G182" s="68"/>
     </row>
-    <row r="183" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A183" s="16"/>
       <c r="B183" s="19" t="s">
         <v>115</v>
@@ -4608,7 +4608,7 @@
       <c r="F183" s="65"/>
       <c r="G183" s="68"/>
     </row>
-    <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="16"/>
       <c r="B184" s="19" t="s">
         <v>153</v>
@@ -4619,7 +4619,7 @@
       <c r="F184" s="66"/>
       <c r="G184" s="69"/>
     </row>
-    <row r="185" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A185" s="16">
         <v>2</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="16"/>
       <c r="B186" s="18" t="s">
         <v>87</v>
@@ -4650,7 +4650,7 @@
       <c r="F186" s="65"/>
       <c r="G186" s="68"/>
     </row>
-    <row r="187" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="16"/>
       <c r="B187" s="19" t="s">
         <v>16</v>
@@ -4666,7 +4666,7 @@
       <c r="F187" s="65"/>
       <c r="G187" s="68"/>
     </row>
-    <row r="188" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="16"/>
       <c r="B188" s="19" t="s">
         <v>150</v>
@@ -4682,7 +4682,7 @@
       <c r="F188" s="65"/>
       <c r="G188" s="68"/>
     </row>
-    <row r="189" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="16"/>
       <c r="B189" s="18" t="s">
         <v>88</v>
@@ -4693,7 +4693,7 @@
       <c r="F189" s="65"/>
       <c r="G189" s="68"/>
     </row>
-    <row r="190" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="19" t="s">
         <v>155</v>
@@ -4704,7 +4704,7 @@
       <c r="F190" s="65"/>
       <c r="G190" s="68"/>
     </row>
-    <row r="191" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A191" s="16"/>
       <c r="B191" s="19" t="s">
         <v>156</v>
@@ -4715,7 +4715,7 @@
       <c r="F191" s="65"/>
       <c r="G191" s="68"/>
     </row>
-    <row r="192" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="16"/>
       <c r="B192" s="19" t="s">
         <v>157</v>
@@ -4726,7 +4726,7 @@
       <c r="F192" s="66"/>
       <c r="G192" s="69"/>
     </row>
-    <row r="193" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="22">
         <v>3</v>
       </c>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D193" s="77">
         <f>('Исходные данные'!D19+'Исходные данные'!D2)/100</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E193" s="78"/>
       <c r="F193" s="25"/>
@@ -4746,7 +4746,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="27"/>
       <c r="B194" s="28"/>
       <c r="C194" s="27"/>
@@ -4755,7 +4755,7 @@
       <c r="F194" s="28"/>
       <c r="G194" s="27"/>
     </row>
-    <row r="195" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="21"/>
       <c r="B195" s="21"/>
       <c r="C195" s="79" t="s">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="G195" s="27"/>
     </row>
-    <row r="196" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="21"/>
       <c r="B196" s="21"/>
       <c r="C196" s="21"/>
@@ -4777,7 +4777,7 @@
       <c r="F196" s="21"/>
       <c r="G196" s="27"/>
     </row>
-    <row r="197" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="21"/>
       <c r="B197" s="21"/>
       <c r="C197" s="79" t="s">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G197" s="27"/>
     </row>
-    <row r="198" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="21"/>
       <c r="B198" s="21"/>
       <c r="C198" s="21"/>
@@ -4799,7 +4799,7 @@
       <c r="F198" s="33"/>
       <c r="G198" s="27"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="34"/>
       <c r="B199" s="34"/>
       <c r="C199" s="34"/>
@@ -4807,7 +4807,7 @@
       <c r="E199" s="34"/>
       <c r="F199" s="35"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="36"/>
       <c r="B200" s="36"/>
       <c r="C200" s="36"/>
@@ -4816,7 +4816,7 @@
       <c r="F200" s="36"/>
       <c r="G200" s="36"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="36"/>
       <c r="B201" s="36"/>
       <c r="C201" s="36"/>
@@ -4825,7 +4825,7 @@
       <c r="F201" s="36"/>
       <c r="G201" s="36"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="36"/>
       <c r="B202" s="36"/>
       <c r="C202" s="36"/>
@@ -4834,7 +4834,7 @@
       <c r="F202" s="36"/>
       <c r="G202" s="36"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="36"/>
       <c r="B203" s="36"/>
       <c r="C203" s="36"/>
@@ -4843,7 +4843,7 @@
       <c r="F203" s="36"/>
       <c r="G203" s="36"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="36"/>
       <c r="B204" s="36"/>
       <c r="C204" s="36"/>
@@ -4852,7 +4852,7 @@
       <c r="F204" s="36"/>
       <c r="G204" s="36"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="36"/>
       <c r="B205" s="36"/>
       <c r="C205" s="36"/>
@@ -4861,7 +4861,7 @@
       <c r="F205" s="36"/>
       <c r="G205" s="36"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="36"/>
       <c r="B206" s="36"/>
       <c r="C206" s="36"/>
@@ -4870,7 +4870,7 @@
       <c r="F206" s="36"/>
       <c r="G206" s="36"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="36"/>
       <c r="B207" s="36"/>
       <c r="C207" s="36"/>
@@ -4879,7 +4879,7 @@
       <c r="F207" s="36"/>
       <c r="G207" s="36"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="34"/>
       <c r="B208" s="34"/>
       <c r="C208" s="34"/>
@@ -4887,7 +4887,7 @@
       <c r="E208" s="34"/>
       <c r="F208" s="35"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="34"/>
       <c r="B209" s="34"/>
       <c r="C209" s="34"/>
@@ -4895,7 +4895,7 @@
       <c r="E209" s="34"/>
       <c r="F209" s="35"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="34"/>
       <c r="B210" s="34"/>
       <c r="C210" s="34"/>
@@ -4903,7 +4903,7 @@
       <c r="E210" s="34"/>
       <c r="F210" s="35"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="34"/>
       <c r="B211" s="34"/>
       <c r="C211" s="34"/>
@@ -4911,7 +4911,7 @@
       <c r="E211" s="34"/>
       <c r="F211" s="35"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="34"/>
       <c r="B212" s="34"/>
       <c r="C212" s="34"/>
@@ -4919,7 +4919,7 @@
       <c r="E212" s="34"/>
       <c r="F212" s="35"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="34"/>
       <c r="B213" s="34"/>
       <c r="C213" s="34"/>
@@ -4927,7 +4927,7 @@
       <c r="E213" s="34"/>
       <c r="F213" s="35"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="34"/>
       <c r="B214" s="34"/>
       <c r="C214" s="34"/>
@@ -4935,7 +4935,7 @@
       <c r="E214" s="34"/>
       <c r="F214" s="35"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="34"/>
       <c r="B215" s="34"/>
       <c r="C215" s="34"/>
@@ -4943,7 +4943,7 @@
       <c r="E215" s="34"/>
       <c r="F215" s="35"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="34"/>
       <c r="B216" s="34"/>
       <c r="C216" s="34"/>
@@ -4951,7 +4951,7 @@
       <c r="E216" s="34"/>
       <c r="F216" s="35"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="34"/>
       <c r="B217" s="34"/>
       <c r="C217" s="34"/>
@@ -4959,7 +4959,7 @@
       <c r="E217" s="34"/>
       <c r="F217" s="35"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="34"/>
       <c r="B218" s="34"/>
       <c r="C218" s="34"/>
@@ -4967,7 +4967,7 @@
       <c r="E218" s="34"/>
       <c r="F218" s="35"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="34"/>
       <c r="B219" s="34"/>
       <c r="C219" s="34"/>
@@ -4975,7 +4975,7 @@
       <c r="E219" s="34"/>
       <c r="F219" s="35"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="34"/>
       <c r="B220" s="34"/>
       <c r="C220" s="34"/>
@@ -4983,7 +4983,7 @@
       <c r="E220" s="34"/>
       <c r="F220" s="35"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="34"/>
       <c r="B221" s="34"/>
       <c r="C221" s="34"/>
@@ -4991,7 +4991,7 @@
       <c r="E221" s="34"/>
       <c r="F221" s="35"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="34"/>
       <c r="B222" s="34"/>
       <c r="C222" s="34"/>
@@ -4999,7 +4999,7 @@
       <c r="E222" s="34"/>
       <c r="F222" s="35"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="34"/>
       <c r="B223" s="34"/>
       <c r="C223" s="34"/>
@@ -5007,7 +5007,7 @@
       <c r="E223" s="34"/>
       <c r="F223" s="35"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="34"/>
       <c r="B224" s="34"/>
       <c r="C224" s="34"/>
@@ -5015,7 +5015,7 @@
       <c r="E224" s="34"/>
       <c r="F224" s="35"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="34"/>
       <c r="B225" s="34"/>
       <c r="C225" s="34"/>
@@ -5023,7 +5023,7 @@
       <c r="E225" s="34"/>
       <c r="F225" s="35"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="34"/>
       <c r="B226" s="34"/>
       <c r="C226" s="34"/>
@@ -5031,7 +5031,7 @@
       <c r="E226" s="34"/>
       <c r="F226" s="35"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="34"/>
       <c r="B227" s="34"/>
       <c r="C227" s="34"/>
@@ -5039,7 +5039,7 @@
       <c r="E227" s="34"/>
       <c r="F227" s="35"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="34"/>
       <c r="B228" s="34"/>
       <c r="C228" s="34"/>
@@ -5047,7 +5047,7 @@
       <c r="E228" s="34"/>
       <c r="F228" s="35"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="34"/>
       <c r="B229" s="34"/>
       <c r="C229" s="34"/>
@@ -5055,7 +5055,7 @@
       <c r="E229" s="34"/>
       <c r="F229" s="35"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="34"/>
       <c r="B230" s="34"/>
       <c r="C230" s="34"/>
@@ -5063,7 +5063,7 @@
       <c r="E230" s="34"/>
       <c r="F230" s="35"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="34"/>
       <c r="B231" s="34"/>
       <c r="C231" s="34"/>
@@ -5071,7 +5071,7 @@
       <c r="E231" s="34"/>
       <c r="F231" s="35"/>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="34"/>
       <c r="B232" s="34"/>
       <c r="C232" s="34"/>
@@ -5079,7 +5079,7 @@
       <c r="E232" s="34"/>
       <c r="F232" s="35"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="34"/>
       <c r="B233" s="34"/>
       <c r="C233" s="34"/>
@@ -5087,7 +5087,7 @@
       <c r="E233" s="34"/>
       <c r="F233" s="35"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="34"/>
       <c r="B234" s="34"/>
       <c r="C234" s="34"/>
@@ -5095,7 +5095,7 @@
       <c r="E234" s="34"/>
       <c r="F234" s="35"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="34"/>
       <c r="B235" s="34"/>
       <c r="C235" s="34"/>
@@ -5103,7 +5103,7 @@
       <c r="E235" s="34"/>
       <c r="F235" s="35"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="34"/>
       <c r="B236" s="34"/>
       <c r="C236" s="34"/>
@@ -5111,7 +5111,7 @@
       <c r="E236" s="34"/>
       <c r="F236" s="35"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="34"/>
       <c r="B237" s="34"/>
       <c r="C237" s="34"/>
@@ -5119,7 +5119,7 @@
       <c r="E237" s="34"/>
       <c r="F237" s="35"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="34"/>
       <c r="B238" s="34"/>
       <c r="C238" s="34"/>
@@ -5127,7 +5127,7 @@
       <c r="E238" s="34"/>
       <c r="F238" s="35"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="34"/>
       <c r="B239" s="34"/>
       <c r="C239" s="34"/>
@@ -5135,7 +5135,7 @@
       <c r="E239" s="34"/>
       <c r="F239" s="35"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="34"/>
       <c r="B240" s="34"/>
       <c r="C240" s="34"/>
@@ -5143,7 +5143,7 @@
       <c r="E240" s="34"/>
       <c r="F240" s="35"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="34"/>
       <c r="B241" s="34"/>
       <c r="C241" s="34"/>
@@ -5151,7 +5151,7 @@
       <c r="E241" s="34"/>
       <c r="F241" s="35"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="34"/>
       <c r="B242" s="34"/>
       <c r="C242" s="34"/>
@@ -5159,7 +5159,7 @@
       <c r="E242" s="34"/>
       <c r="F242" s="35"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="34"/>
       <c r="B243" s="34"/>
       <c r="C243" s="34"/>
@@ -5167,7 +5167,7 @@
       <c r="E243" s="34"/>
       <c r="F243" s="35"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="34"/>
       <c r="B244" s="34"/>
       <c r="C244" s="34"/>
@@ -5175,7 +5175,7 @@
       <c r="E244" s="34"/>
       <c r="F244" s="35"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="34"/>
       <c r="B245" s="34"/>
       <c r="C245" s="34"/>
@@ -5183,7 +5183,7 @@
       <c r="E245" s="34"/>
       <c r="F245" s="35"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="34"/>
       <c r="B246" s="34"/>
       <c r="C246" s="34"/>
@@ -5191,7 +5191,7 @@
       <c r="E246" s="34"/>
       <c r="F246" s="35"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="34"/>
       <c r="B247" s="34"/>
       <c r="C247" s="34"/>
@@ -5199,7 +5199,7 @@
       <c r="E247" s="34"/>
       <c r="F247" s="35"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="34"/>
       <c r="B248" s="34"/>
       <c r="C248" s="34"/>
@@ -5207,7 +5207,7 @@
       <c r="E248" s="34"/>
       <c r="F248" s="35"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="34"/>
       <c r="B249" s="34"/>
       <c r="C249" s="34"/>
@@ -5215,7 +5215,7 @@
       <c r="E249" s="34"/>
       <c r="F249" s="35"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="34"/>
       <c r="B250" s="34"/>
       <c r="C250" s="34"/>
@@ -5223,7 +5223,7 @@
       <c r="E250" s="34"/>
       <c r="F250" s="35"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="34"/>
       <c r="B251" s="34"/>
       <c r="C251" s="34"/>
@@ -5231,7 +5231,7 @@
       <c r="E251" s="34"/>
       <c r="F251" s="35"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="34"/>
       <c r="B252" s="34"/>
       <c r="C252" s="34"/>
@@ -5239,7 +5239,7 @@
       <c r="E252" s="34"/>
       <c r="F252" s="35"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="34"/>
       <c r="B253" s="34"/>
       <c r="C253" s="34"/>
@@ -5247,7 +5247,7 @@
       <c r="E253" s="34"/>
       <c r="F253" s="35"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="34"/>
       <c r="B254" s="34"/>
       <c r="C254" s="34"/>
@@ -5255,7 +5255,7 @@
       <c r="E254" s="34"/>
       <c r="F254" s="35"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="34"/>
       <c r="B255" s="34"/>
       <c r="C255" s="34"/>
@@ -5263,7 +5263,7 @@
       <c r="E255" s="34"/>
       <c r="F255" s="35"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="34"/>
       <c r="B256" s="34"/>
       <c r="C256" s="34"/>
@@ -5271,7 +5271,7 @@
       <c r="E256" s="34"/>
       <c r="F256" s="35"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="34"/>
       <c r="B257" s="34"/>
       <c r="C257" s="34"/>
@@ -5279,7 +5279,7 @@
       <c r="E257" s="34"/>
       <c r="F257" s="35"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="34"/>
       <c r="B258" s="34"/>
       <c r="C258" s="34"/>
@@ -5287,7 +5287,7 @@
       <c r="E258" s="34"/>
       <c r="F258" s="35"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="34"/>
       <c r="B259" s="34"/>
       <c r="C259" s="34"/>
@@ -5295,7 +5295,7 @@
       <c r="E259" s="34"/>
       <c r="F259" s="35"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="34"/>
       <c r="B260" s="34"/>
       <c r="C260" s="34"/>
@@ -5303,7 +5303,7 @@
       <c r="E260" s="34"/>
       <c r="F260" s="35"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="34"/>
       <c r="B261" s="34"/>
       <c r="C261" s="34"/>
@@ -5311,7 +5311,7 @@
       <c r="E261" s="34"/>
       <c r="F261" s="35"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="34"/>
       <c r="B262" s="34"/>
       <c r="C262" s="34"/>
@@ -5319,7 +5319,7 @@
       <c r="E262" s="34"/>
       <c r="F262" s="35"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="34"/>
       <c r="B263" s="34"/>
       <c r="C263" s="34"/>
@@ -5327,7 +5327,7 @@
       <c r="E263" s="34"/>
       <c r="F263" s="35"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="34"/>
       <c r="B264" s="34"/>
       <c r="C264" s="34"/>
@@ -5335,7 +5335,7 @@
       <c r="E264" s="34"/>
       <c r="F264" s="35"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="34"/>
       <c r="B265" s="34"/>
       <c r="C265" s="34"/>
@@ -5343,7 +5343,7 @@
       <c r="E265" s="34"/>
       <c r="F265" s="35"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="34"/>
       <c r="B266" s="34"/>
       <c r="C266" s="34"/>
@@ -5351,7 +5351,7 @@
       <c r="E266" s="34"/>
       <c r="F266" s="35"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="34"/>
       <c r="B267" s="34"/>
       <c r="C267" s="34"/>
@@ -5359,7 +5359,7 @@
       <c r="E267" s="34"/>
       <c r="F267" s="35"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="34"/>
       <c r="B268" s="34"/>
       <c r="C268" s="34"/>
@@ -5367,7 +5367,7 @@
       <c r="E268" s="34"/>
       <c r="F268" s="35"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="34"/>
       <c r="B269" s="34"/>
       <c r="C269" s="34"/>
@@ -5375,7 +5375,7 @@
       <c r="E269" s="34"/>
       <c r="F269" s="35"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="34"/>
       <c r="B270" s="34"/>
       <c r="C270" s="34"/>
@@ -5383,7 +5383,7 @@
       <c r="E270" s="34"/>
       <c r="F270" s="35"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="34"/>
       <c r="B271" s="34"/>
       <c r="C271" s="34"/>
@@ -5391,7 +5391,7 @@
       <c r="E271" s="34"/>
       <c r="F271" s="35"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="34"/>
       <c r="B272" s="34"/>
       <c r="C272" s="34"/>
@@ -5399,7 +5399,7 @@
       <c r="E272" s="34"/>
       <c r="F272" s="35"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="34"/>
       <c r="B273" s="34"/>
       <c r="C273" s="34"/>
@@ -5407,7 +5407,7 @@
       <c r="E273" s="34"/>
       <c r="F273" s="35"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="34"/>
       <c r="B274" s="34"/>
       <c r="C274" s="34"/>
@@ -5415,7 +5415,7 @@
       <c r="E274" s="34"/>
       <c r="F274" s="35"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="34"/>
       <c r="B275" s="34"/>
       <c r="C275" s="34"/>
@@ -5423,7 +5423,7 @@
       <c r="E275" s="34"/>
       <c r="F275" s="35"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="34"/>
       <c r="B276" s="34"/>
       <c r="C276" s="34"/>
@@ -5431,7 +5431,7 @@
       <c r="E276" s="34"/>
       <c r="F276" s="35"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="34"/>
       <c r="B277" s="34"/>
       <c r="C277" s="34"/>
@@ -5439,7 +5439,7 @@
       <c r="E277" s="34"/>
       <c r="F277" s="35"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="34"/>
       <c r="B278" s="34"/>
       <c r="C278" s="34"/>
@@ -5447,7 +5447,7 @@
       <c r="E278" s="34"/>
       <c r="F278" s="35"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="34"/>
       <c r="B279" s="34"/>
       <c r="C279" s="34"/>
@@ -5455,7 +5455,7 @@
       <c r="E279" s="34"/>
       <c r="F279" s="35"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="34"/>
       <c r="B280" s="34"/>
       <c r="C280" s="34"/>
@@ -5463,7 +5463,7 @@
       <c r="E280" s="34"/>
       <c r="F280" s="35"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="34"/>
       <c r="B281" s="34"/>
       <c r="C281" s="34"/>
@@ -5471,7 +5471,7 @@
       <c r="E281" s="34"/>
       <c r="F281" s="35"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="34"/>
       <c r="B282" s="34"/>
       <c r="C282" s="34"/>
@@ -5479,7 +5479,7 @@
       <c r="E282" s="34"/>
       <c r="F282" s="35"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="34"/>
       <c r="B283" s="34"/>
       <c r="C283" s="34"/>
@@ -5487,7 +5487,7 @@
       <c r="E283" s="34"/>
       <c r="F283" s="35"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="34"/>
       <c r="B284" s="34"/>
       <c r="C284" s="34"/>
@@ -5495,7 +5495,7 @@
       <c r="E284" s="34"/>
       <c r="F284" s="35"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="34"/>
       <c r="B285" s="34"/>
       <c r="C285" s="34"/>
@@ -5503,7 +5503,7 @@
       <c r="E285" s="34"/>
       <c r="F285" s="35"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="34"/>
       <c r="B286" s="34"/>
       <c r="C286" s="34"/>
@@ -5511,7 +5511,7 @@
       <c r="E286" s="34"/>
       <c r="F286" s="35"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="34"/>
       <c r="B287" s="34"/>
       <c r="C287" s="34"/>
@@ -5519,7 +5519,7 @@
       <c r="E287" s="34"/>
       <c r="F287" s="35"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="34"/>
       <c r="B288" s="34"/>
       <c r="C288" s="34"/>
@@ -5527,7 +5527,7 @@
       <c r="E288" s="34"/>
       <c r="F288" s="35"/>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="34"/>
       <c r="B289" s="34"/>
       <c r="C289" s="34"/>
@@ -5535,7 +5535,7 @@
       <c r="E289" s="34"/>
       <c r="F289" s="35"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="34"/>
       <c r="B290" s="34"/>
       <c r="C290" s="34"/>
@@ -5543,7 +5543,7 @@
       <c r="E290" s="34"/>
       <c r="F290" s="35"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="34"/>
       <c r="B291" s="34"/>
       <c r="C291" s="34"/>
@@ -5551,7 +5551,7 @@
       <c r="E291" s="34"/>
       <c r="F291" s="35"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="34"/>
       <c r="B292" s="34"/>
       <c r="C292" s="34"/>
@@ -5559,7 +5559,7 @@
       <c r="E292" s="34"/>
       <c r="F292" s="35"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="34"/>
       <c r="B293" s="34"/>
       <c r="C293" s="34"/>
@@ -5567,7 +5567,7 @@
       <c r="E293" s="34"/>
       <c r="F293" s="35"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="34"/>
       <c r="B294" s="34"/>
       <c r="C294" s="34"/>
@@ -5575,7 +5575,7 @@
       <c r="E294" s="34"/>
       <c r="F294" s="35"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="34"/>
       <c r="B295" s="34"/>
       <c r="C295" s="34"/>
@@ -5583,7 +5583,7 @@
       <c r="E295" s="34"/>
       <c r="F295" s="35"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="34"/>
       <c r="B296" s="34"/>
       <c r="C296" s="34"/>
@@ -5591,7 +5591,7 @@
       <c r="E296" s="34"/>
       <c r="F296" s="35"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="37"/>
       <c r="B297" s="37"/>
       <c r="C297" s="37"/>
@@ -5599,7 +5599,7 @@
       <c r="E297" s="37"/>
       <c r="F297" s="38"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="37"/>
       <c r="B298" s="37"/>
       <c r="C298" s="37"/>
@@ -5607,7 +5607,7 @@
       <c r="E298" s="37"/>
       <c r="F298" s="38"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="37"/>
       <c r="B299" s="37"/>
       <c r="C299" s="37"/>
@@ -5615,7 +5615,7 @@
       <c r="E299" s="37"/>
       <c r="F299" s="38"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="37"/>
       <c r="B300" s="37"/>
       <c r="C300" s="37"/>
@@ -5623,7 +5623,7 @@
       <c r="E300" s="37"/>
       <c r="F300" s="38"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="37"/>
       <c r="B301" s="37"/>
       <c r="C301" s="37"/>
@@ -5631,7 +5631,7 @@
       <c r="E301" s="37"/>
       <c r="F301" s="38"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="37"/>
       <c r="B302" s="37"/>
       <c r="C302" s="37"/>
@@ -5639,7 +5639,7 @@
       <c r="E302" s="37"/>
       <c r="F302" s="38"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="37"/>
       <c r="B303" s="37"/>
       <c r="C303" s="37"/>
@@ -5647,7 +5647,7 @@
       <c r="E303" s="37"/>
       <c r="F303" s="38"/>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="37"/>
       <c r="B304" s="37"/>
       <c r="C304" s="37"/>
@@ -5655,7 +5655,7 @@
       <c r="E304" s="37"/>
       <c r="F304" s="38"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="37"/>
       <c r="B305" s="37"/>
       <c r="C305" s="37"/>
@@ -5663,7 +5663,7 @@
       <c r="E305" s="37"/>
       <c r="F305" s="38"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="37"/>
       <c r="B306" s="37"/>
       <c r="C306" s="37"/>
@@ -5671,7 +5671,7 @@
       <c r="E306" s="37"/>
       <c r="F306" s="38"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="37"/>
       <c r="B307" s="37"/>
       <c r="C307" s="37"/>
@@ -5679,7 +5679,7 @@
       <c r="E307" s="37"/>
       <c r="F307" s="38"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="37"/>
       <c r="B308" s="37"/>
       <c r="C308" s="37"/>
@@ -5687,7 +5687,7 @@
       <c r="E308" s="37"/>
       <c r="F308" s="38"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="37"/>
       <c r="B309" s="37"/>
       <c r="C309" s="37"/>
@@ -5695,7 +5695,7 @@
       <c r="E309" s="37"/>
       <c r="F309" s="38"/>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="37"/>
       <c r="B310" s="37"/>
       <c r="C310" s="37"/>
@@ -5703,7 +5703,7 @@
       <c r="E310" s="37"/>
       <c r="F310" s="38"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="37"/>
       <c r="B311" s="37"/>
       <c r="C311" s="37"/>
@@ -5711,7 +5711,7 @@
       <c r="E311" s="37"/>
       <c r="F311" s="38"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="37"/>
       <c r="B312" s="37"/>
       <c r="C312" s="37"/>
@@ -5719,7 +5719,7 @@
       <c r="E312" s="37"/>
       <c r="F312" s="38"/>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="37"/>
       <c r="B313" s="37"/>
       <c r="C313" s="37"/>
@@ -5727,7 +5727,7 @@
       <c r="E313" s="37"/>
       <c r="F313" s="38"/>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="37"/>
       <c r="B314" s="37"/>
       <c r="C314" s="37"/>
@@ -5735,7 +5735,7 @@
       <c r="E314" s="37"/>
       <c r="F314" s="38"/>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="37"/>
       <c r="B315" s="37"/>
       <c r="C315" s="37"/>
@@ -5743,7 +5743,7 @@
       <c r="E315" s="37"/>
       <c r="F315" s="38"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="37"/>
       <c r="B316" s="37"/>
       <c r="C316" s="37"/>
@@ -5751,7 +5751,7 @@
       <c r="E316" s="37"/>
       <c r="F316" s="38"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="37"/>
       <c r="B317" s="37"/>
       <c r="C317" s="37"/>
@@ -5759,7 +5759,7 @@
       <c r="E317" s="37"/>
       <c r="F317" s="38"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="37"/>
       <c r="B318" s="37"/>
       <c r="C318" s="37"/>
@@ -5767,7 +5767,7 @@
       <c r="E318" s="37"/>
       <c r="F318" s="38"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="37"/>
       <c r="B319" s="37"/>
       <c r="C319" s="37"/>
@@ -5775,7 +5775,7 @@
       <c r="E319" s="37"/>
       <c r="F319" s="38"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="37"/>
       <c r="B320" s="37"/>
       <c r="C320" s="37"/>
@@ -5783,7 +5783,7 @@
       <c r="E320" s="37"/>
       <c r="F320" s="38"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="37"/>
       <c r="B321" s="37"/>
       <c r="C321" s="37"/>
@@ -5791,7 +5791,7 @@
       <c r="E321" s="37"/>
       <c r="F321" s="38"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="37"/>
       <c r="B322" s="37"/>
       <c r="C322" s="37"/>
@@ -5799,7 +5799,7 @@
       <c r="E322" s="37"/>
       <c r="F322" s="38"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="37"/>
       <c r="B323" s="37"/>
       <c r="C323" s="37"/>
@@ -5807,7 +5807,7 @@
       <c r="E323" s="37"/>
       <c r="F323" s="38"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="37"/>
       <c r="B324" s="37"/>
       <c r="C324" s="37"/>
@@ -5815,7 +5815,7 @@
       <c r="E324" s="37"/>
       <c r="F324" s="38"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="37"/>
       <c r="B325" s="37"/>
       <c r="C325" s="37"/>
@@ -5823,7 +5823,7 @@
       <c r="E325" s="37"/>
       <c r="F325" s="38"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="37"/>
       <c r="B326" s="37"/>
       <c r="C326" s="37"/>
@@ -5831,7 +5831,7 @@
       <c r="E326" s="37"/>
       <c r="F326" s="38"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="37"/>
       <c r="B327" s="37"/>
       <c r="C327" s="37"/>
@@ -5839,7 +5839,7 @@
       <c r="E327" s="37"/>
       <c r="F327" s="38"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="37"/>
       <c r="B328" s="37"/>
       <c r="C328" s="37"/>
@@ -5847,7 +5847,7 @@
       <c r="E328" s="37"/>
       <c r="F328" s="38"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="37"/>
       <c r="B329" s="37"/>
       <c r="C329" s="37"/>
@@ -5855,7 +5855,7 @@
       <c r="E329" s="37"/>
       <c r="F329" s="38"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="37"/>
       <c r="B330" s="37"/>
       <c r="C330" s="37"/>
@@ -5863,7 +5863,7 @@
       <c r="E330" s="37"/>
       <c r="F330" s="38"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="37"/>
       <c r="B331" s="37"/>
       <c r="C331" s="37"/>
@@ -5871,7 +5871,7 @@
       <c r="E331" s="37"/>
       <c r="F331" s="38"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="37"/>
       <c r="B332" s="37"/>
       <c r="C332" s="37"/>
@@ -5879,7 +5879,7 @@
       <c r="E332" s="37"/>
       <c r="F332" s="38"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="37"/>
       <c r="B333" s="37"/>
       <c r="C333" s="37"/>
@@ -5887,7 +5887,7 @@
       <c r="E333" s="37"/>
       <c r="F333" s="38"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="37"/>
       <c r="B334" s="37"/>
       <c r="C334" s="37"/>
@@ -5895,7 +5895,7 @@
       <c r="E334" s="37"/>
       <c r="F334" s="38"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="37"/>
       <c r="B335" s="37"/>
       <c r="C335" s="37"/>
@@ -5903,7 +5903,7 @@
       <c r="E335" s="37"/>
       <c r="F335" s="38"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="37"/>
       <c r="B336" s="37"/>
       <c r="C336" s="37"/>
@@ -5911,7 +5911,7 @@
       <c r="E336" s="37"/>
       <c r="F336" s="38"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="37"/>
       <c r="B337" s="37"/>
       <c r="C337" s="37"/>
@@ -5919,7 +5919,7 @@
       <c r="E337" s="37"/>
       <c r="F337" s="38"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="37"/>
       <c r="B338" s="37"/>
       <c r="C338" s="37"/>
@@ -5927,7 +5927,7 @@
       <c r="E338" s="37"/>
       <c r="F338" s="38"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="37"/>
       <c r="B339" s="37"/>
       <c r="C339" s="37"/>
@@ -5935,7 +5935,7 @@
       <c r="E339" s="37"/>
       <c r="F339" s="38"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="37"/>
       <c r="B340" s="37"/>
       <c r="C340" s="37"/>
@@ -5943,7 +5943,7 @@
       <c r="E340" s="37"/>
       <c r="F340" s="38"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="37"/>
       <c r="B341" s="37"/>
       <c r="C341" s="37"/>
@@ -5951,7 +5951,7 @@
       <c r="E341" s="37"/>
       <c r="F341" s="38"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="37"/>
       <c r="B342" s="37"/>
       <c r="C342" s="37"/>
@@ -5959,7 +5959,7 @@
       <c r="E342" s="37"/>
       <c r="F342" s="38"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="37"/>
       <c r="B343" s="37"/>
       <c r="C343" s="37"/>
@@ -5967,7 +5967,7 @@
       <c r="E343" s="37"/>
       <c r="F343" s="38"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="37"/>
       <c r="B344" s="37"/>
       <c r="C344" s="37"/>
@@ -5975,7 +5975,7 @@
       <c r="E344" s="37"/>
       <c r="F344" s="38"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="37"/>
       <c r="B345" s="37"/>
       <c r="C345" s="37"/>
@@ -5983,7 +5983,7 @@
       <c r="E345" s="37"/>
       <c r="F345" s="38"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="37"/>
       <c r="B346" s="37"/>
       <c r="C346" s="37"/>
@@ -5991,7 +5991,7 @@
       <c r="E346" s="37"/>
       <c r="F346" s="38"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="37"/>
       <c r="B347" s="37"/>
       <c r="C347" s="37"/>
@@ -5999,7 +5999,7 @@
       <c r="E347" s="37"/>
       <c r="F347" s="38"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="37"/>
       <c r="B348" s="37"/>
       <c r="C348" s="37"/>
@@ -6007,7 +6007,7 @@
       <c r="E348" s="37"/>
       <c r="F348" s="38"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="37"/>
       <c r="B349" s="37"/>
       <c r="C349" s="37"/>
@@ -6015,7 +6015,7 @@
       <c r="E349" s="37"/>
       <c r="F349" s="38"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="37"/>
       <c r="B350" s="37"/>
       <c r="C350" s="37"/>
@@ -6023,7 +6023,7 @@
       <c r="E350" s="37"/>
       <c r="F350" s="38"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="37"/>
       <c r="B351" s="37"/>
       <c r="C351" s="37"/>
@@ -6031,7 +6031,7 @@
       <c r="E351" s="37"/>
       <c r="F351" s="38"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="37"/>
       <c r="B352" s="37"/>
       <c r="C352" s="37"/>
@@ -6039,7 +6039,7 @@
       <c r="E352" s="37"/>
       <c r="F352" s="38"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="37"/>
       <c r="B353" s="37"/>
       <c r="C353" s="37"/>
@@ -6047,7 +6047,7 @@
       <c r="E353" s="37"/>
       <c r="F353" s="38"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="37"/>
       <c r="B354" s="37"/>
       <c r="C354" s="37"/>
@@ -6055,7 +6055,7 @@
       <c r="E354" s="37"/>
       <c r="F354" s="38"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="37"/>
       <c r="B355" s="37"/>
       <c r="C355" s="37"/>
@@ -6063,7 +6063,7 @@
       <c r="E355" s="37"/>
       <c r="F355" s="38"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="37"/>
       <c r="B356" s="37"/>
       <c r="C356" s="37"/>
@@ -6071,7 +6071,7 @@
       <c r="E356" s="37"/>
       <c r="F356" s="38"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="37"/>
       <c r="B357" s="37"/>
       <c r="C357" s="37"/>
@@ -6079,7 +6079,7 @@
       <c r="E357" s="37"/>
       <c r="F357" s="38"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="37"/>
       <c r="B358" s="37"/>
       <c r="C358" s="37"/>
@@ -6087,7 +6087,7 @@
       <c r="E358" s="37"/>
       <c r="F358" s="38"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="37"/>
       <c r="B359" s="37"/>
       <c r="C359" s="37"/>
@@ -6095,7 +6095,7 @@
       <c r="E359" s="37"/>
       <c r="F359" s="38"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="37"/>
       <c r="B360" s="37"/>
       <c r="C360" s="37"/>
@@ -6103,7 +6103,7 @@
       <c r="E360" s="37"/>
       <c r="F360" s="38"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="37"/>
       <c r="B361" s="37"/>
       <c r="C361" s="37"/>
@@ -6111,7 +6111,7 @@
       <c r="E361" s="37"/>
       <c r="F361" s="38"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" s="37"/>
       <c r="B362" s="37"/>
       <c r="C362" s="37"/>
@@ -6119,7 +6119,7 @@
       <c r="E362" s="37"/>
       <c r="F362" s="38"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="37"/>
       <c r="B363" s="37"/>
       <c r="C363" s="37"/>
@@ -6127,7 +6127,7 @@
       <c r="E363" s="37"/>
       <c r="F363" s="38"/>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="37"/>
       <c r="B364" s="37"/>
       <c r="C364" s="37"/>
@@ -6135,7 +6135,7 @@
       <c r="E364" s="37"/>
       <c r="F364" s="38"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="37"/>
       <c r="B365" s="37"/>
       <c r="C365" s="37"/>
@@ -6143,7 +6143,7 @@
       <c r="E365" s="37"/>
       <c r="F365" s="38"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="37"/>
       <c r="B366" s="37"/>
       <c r="C366" s="37"/>
@@ -6151,7 +6151,7 @@
       <c r="E366" s="37"/>
       <c r="F366" s="38"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="37"/>
       <c r="B367" s="37"/>
       <c r="C367" s="37"/>
@@ -6159,7 +6159,7 @@
       <c r="E367" s="37"/>
       <c r="F367" s="38"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="37"/>
       <c r="B368" s="37"/>
       <c r="C368" s="37"/>
@@ -6167,7 +6167,7 @@
       <c r="E368" s="37"/>
       <c r="F368" s="38"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="37"/>
       <c r="B369" s="37"/>
       <c r="C369" s="37"/>
@@ -6175,7 +6175,7 @@
       <c r="E369" s="37"/>
       <c r="F369" s="38"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="37"/>
       <c r="B370" s="37"/>
       <c r="C370" s="37"/>
@@ -6183,7 +6183,7 @@
       <c r="E370" s="37"/>
       <c r="F370" s="38"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="37"/>
       <c r="B371" s="37"/>
       <c r="C371" s="37"/>
@@ -6191,7 +6191,7 @@
       <c r="E371" s="37"/>
       <c r="F371" s="38"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="37"/>
       <c r="B372" s="37"/>
       <c r="C372" s="37"/>
@@ -6199,7 +6199,7 @@
       <c r="E372" s="37"/>
       <c r="F372" s="38"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="37"/>
       <c r="B373" s="37"/>
       <c r="C373" s="37"/>
@@ -6207,7 +6207,7 @@
       <c r="E373" s="37"/>
       <c r="F373" s="38"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="37"/>
       <c r="B374" s="37"/>
       <c r="C374" s="37"/>
@@ -6215,7 +6215,7 @@
       <c r="E374" s="37"/>
       <c r="F374" s="38"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="37"/>
       <c r="B375" s="37"/>
       <c r="C375" s="37"/>
@@ -6223,7 +6223,7 @@
       <c r="E375" s="37"/>
       <c r="F375" s="38"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="37"/>
       <c r="B376" s="37"/>
       <c r="C376" s="37"/>
@@ -6231,7 +6231,7 @@
       <c r="E376" s="37"/>
       <c r="F376" s="38"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="37"/>
       <c r="B377" s="37"/>
       <c r="C377" s="37"/>
@@ -6239,7 +6239,7 @@
       <c r="E377" s="37"/>
       <c r="F377" s="38"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="37"/>
       <c r="B378" s="37"/>
       <c r="C378" s="37"/>
@@ -6247,7 +6247,7 @@
       <c r="E378" s="37"/>
       <c r="F378" s="38"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="37"/>
       <c r="B379" s="37"/>
       <c r="C379" s="37"/>
@@ -6255,7 +6255,7 @@
       <c r="E379" s="37"/>
       <c r="F379" s="38"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="37"/>
       <c r="B380" s="37"/>
       <c r="C380" s="37"/>
@@ -6263,7 +6263,7 @@
       <c r="E380" s="37"/>
       <c r="F380" s="38"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="37"/>
       <c r="B381" s="37"/>
       <c r="C381" s="37"/>
@@ -6271,7 +6271,7 @@
       <c r="E381" s="37"/>
       <c r="F381" s="38"/>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="37"/>
       <c r="B382" s="37"/>
       <c r="C382" s="37"/>
@@ -6279,7 +6279,7 @@
       <c r="E382" s="37"/>
       <c r="F382" s="38"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="37"/>
       <c r="B383" s="37"/>
       <c r="C383" s="37"/>
@@ -6287,7 +6287,7 @@
       <c r="E383" s="37"/>
       <c r="F383" s="38"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="37"/>
       <c r="B384" s="37"/>
       <c r="C384" s="37"/>
@@ -6295,7 +6295,7 @@
       <c r="E384" s="37"/>
       <c r="F384" s="38"/>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="37"/>
       <c r="B385" s="37"/>
       <c r="C385" s="37"/>
@@ -6303,7 +6303,7 @@
       <c r="E385" s="37"/>
       <c r="F385" s="38"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="37"/>
       <c r="B386" s="37"/>
       <c r="C386" s="37"/>
@@ -6311,7 +6311,7 @@
       <c r="E386" s="37"/>
       <c r="F386" s="38"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="37"/>
       <c r="B387" s="37"/>
       <c r="C387" s="37"/>
@@ -6319,7 +6319,7 @@
       <c r="E387" s="37"/>
       <c r="F387" s="38"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="37"/>
       <c r="B388" s="37"/>
       <c r="C388" s="37"/>
@@ -6327,7 +6327,7 @@
       <c r="E388" s="37"/>
       <c r="F388" s="38"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="37"/>
       <c r="B389" s="37"/>
       <c r="C389" s="37"/>
@@ -6335,7 +6335,7 @@
       <c r="E389" s="37"/>
       <c r="F389" s="38"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="37"/>
       <c r="B390" s="37"/>
       <c r="C390" s="37"/>
@@ -6343,7 +6343,7 @@
       <c r="E390" s="37"/>
       <c r="F390" s="38"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="37"/>
       <c r="B391" s="37"/>
       <c r="C391" s="37"/>
@@ -6351,7 +6351,7 @@
       <c r="E391" s="37"/>
       <c r="F391" s="38"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" s="37"/>
       <c r="B392" s="37"/>
       <c r="C392" s="37"/>
@@ -6359,7 +6359,7 @@
       <c r="E392" s="37"/>
       <c r="F392" s="38"/>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" s="37"/>
       <c r="B393" s="37"/>
       <c r="C393" s="37"/>
@@ -6367,7 +6367,7 @@
       <c r="E393" s="37"/>
       <c r="F393" s="38"/>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="37"/>
       <c r="B394" s="37"/>
       <c r="C394" s="37"/>
@@ -6375,7 +6375,7 @@
       <c r="E394" s="37"/>
       <c r="F394" s="38"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="37"/>
       <c r="B395" s="37"/>
       <c r="C395" s="37"/>
@@ -6383,7 +6383,7 @@
       <c r="E395" s="37"/>
       <c r="F395" s="38"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="37"/>
       <c r="B396" s="37"/>
       <c r="C396" s="37"/>
@@ -6391,7 +6391,7 @@
       <c r="E396" s="37"/>
       <c r="F396" s="38"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="37"/>
       <c r="B397" s="37"/>
       <c r="C397" s="37"/>
@@ -6399,7 +6399,7 @@
       <c r="E397" s="37"/>
       <c r="F397" s="38"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="37"/>
       <c r="B398" s="37"/>
       <c r="C398" s="37"/>
@@ -6407,7 +6407,7 @@
       <c r="E398" s="37"/>
       <c r="F398" s="38"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="37"/>
       <c r="B399" s="37"/>
       <c r="C399" s="37"/>
@@ -6415,7 +6415,7 @@
       <c r="E399" s="37"/>
       <c r="F399" s="38"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="37"/>
       <c r="B400" s="37"/>
       <c r="C400" s="37"/>
@@ -6423,7 +6423,7 @@
       <c r="E400" s="37"/>
       <c r="F400" s="38"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="37"/>
       <c r="B401" s="37"/>
       <c r="C401" s="37"/>
@@ -6431,7 +6431,7 @@
       <c r="E401" s="37"/>
       <c r="F401" s="38"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="37"/>
       <c r="B402" s="37"/>
       <c r="C402" s="37"/>
@@ -6439,7 +6439,7 @@
       <c r="E402" s="37"/>
       <c r="F402" s="38"/>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="37"/>
       <c r="B403" s="37"/>
       <c r="C403" s="37"/>
@@ -6447,7 +6447,7 @@
       <c r="E403" s="37"/>
       <c r="F403" s="38"/>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="37"/>
       <c r="B404" s="37"/>
       <c r="C404" s="37"/>
@@ -6455,7 +6455,7 @@
       <c r="E404" s="37"/>
       <c r="F404" s="38"/>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="37"/>
       <c r="B405" s="37"/>
       <c r="C405" s="37"/>
@@ -6463,7 +6463,7 @@
       <c r="E405" s="37"/>
       <c r="F405" s="38"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="37"/>
       <c r="B406" s="37"/>
       <c r="C406" s="37"/>
@@ -6471,7 +6471,7 @@
       <c r="E406" s="37"/>
       <c r="F406" s="38"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="37"/>
       <c r="B407" s="37"/>
       <c r="C407" s="37"/>
@@ -6479,7 +6479,7 @@
       <c r="E407" s="37"/>
       <c r="F407" s="38"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="39"/>
       <c r="B408" s="39"/>
       <c r="C408" s="39"/>
@@ -6487,7 +6487,7 @@
       <c r="E408" s="39"/>
       <c r="F408" s="40"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="39"/>
       <c r="B409" s="39"/>
       <c r="C409" s="39"/>
@@ -6495,7 +6495,7 @@
       <c r="E409" s="39"/>
       <c r="F409" s="40"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="39"/>
       <c r="B410" s="39"/>
       <c r="C410" s="39"/>
@@ -6503,7 +6503,7 @@
       <c r="E410" s="39"/>
       <c r="F410" s="40"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="39"/>
       <c r="B411" s="39"/>
       <c r="C411" s="39"/>
@@ -6511,7 +6511,7 @@
       <c r="E411" s="39"/>
       <c r="F411" s="40"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="39"/>
       <c r="B412" s="39"/>
       <c r="C412" s="39"/>
@@ -6519,7 +6519,7 @@
       <c r="E412" s="39"/>
       <c r="F412" s="40"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="39"/>
       <c r="B413" s="39"/>
       <c r="C413" s="39"/>
@@ -6527,7 +6527,7 @@
       <c r="E413" s="39"/>
       <c r="F413" s="40"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="39"/>
       <c r="B414" s="39"/>
       <c r="C414" s="39"/>
@@ -6618,7 +6618,7 @@
     <mergeCell ref="G3:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="47" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6628,18 +6628,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G454"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="57.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="57.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="40.42578125" customWidth="1"/>
+    <col min="7" max="7" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
         <v>189</v>
       </c>
@@ -6650,7 +6650,7 @@
       <c r="F1" s="47"/>
       <c r="G1" s="48"/>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="49" t="s">
         <v>190</v>
       </c>
@@ -6661,7 +6661,7 @@
       <c r="F2" s="50"/>
       <c r="G2" s="51"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
         <v>0</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="56"/>
       <c r="B4" s="58"/>
       <c r="C4" s="58"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="G4" s="63"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>1</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="52" t="s">
         <v>1</v>
       </c>
@@ -6729,7 +6729,7 @@
       <c r="F6" s="53"/>
       <c r="G6" s="54"/>
     </row>
-    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <v>1</v>
       </c>
@@ -6741,11 +6741,11 @@
       </c>
       <c r="D7" s="3">
         <f>(3.14*('Исходные данные'!B4/2+'Исходные данные'!B5/2)*'Исходные данные'!C3)*1.5/100</f>
-        <v>1.6485000000000002E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="E7" s="3">
         <f>D7*'Исходные данные'!D2</f>
-        <v>4.9455000000000007E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="F7" s="64" t="s">
         <v>33</v>
@@ -6754,7 +6754,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="16"/>
       <c r="B8" s="18" t="s">
         <v>87</v>
@@ -6765,7 +6765,7 @@
       <c r="F8" s="65"/>
       <c r="G8" s="68"/>
     </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="16"/>
       <c r="B9" s="19" t="s">
         <v>10</v>
@@ -6775,16 +6775,16 @@
       </c>
       <c r="D9" s="3">
         <f>0.009*D7</f>
-        <v>1.4836500000000002E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="E9" s="3">
         <f>D9*'Исходные данные'!D2</f>
-        <v>4.4509500000000006E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="F9" s="65"/>
       <c r="G9" s="68"/>
     </row>
-    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="19" t="s">
         <v>11</v>
@@ -6794,16 +6794,16 @@
       </c>
       <c r="D10" s="3">
         <f>0.035*D7</f>
-        <v>5.769750000000001E-7</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="E10" s="3">
         <f>D10*'Исходные данные'!D2</f>
-        <v>1.7309250000000003E-6</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="F10" s="65"/>
       <c r="G10" s="68"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
         <v>8</v>
@@ -6813,16 +6813,16 @@
       </c>
       <c r="D11" s="3">
         <f>3.4*D7</f>
-        <v>5.6049000000000005E-5</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="E11" s="3">
         <f>D11*'Исходные данные'!D2</f>
-        <v>1.68147E-4</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="F11" s="65"/>
       <c r="G11" s="68"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="18" t="s">
         <v>88</v>
@@ -6833,7 +6833,7 @@
       <c r="F12" s="65"/>
       <c r="G12" s="68"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
         <v>90</v>
@@ -6844,7 +6844,7 @@
       <c r="F13" s="66"/>
       <c r="G13" s="69"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="52" t="s">
         <v>119</v>
       </c>
@@ -6855,7 +6855,7 @@
       <c r="F14" s="53"/>
       <c r="G14" s="54"/>
     </row>
-    <row r="15" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <v>1</v>
       </c>
@@ -6867,11 +6867,11 @@
       </c>
       <c r="D15" s="3">
         <f>(3.14*((('Исходные данные'!B4+2)/2)^2-(('Исходные данные'!B4-2)/2)^2))*1/1000</f>
-        <v>1.0048000000000045E-4</v>
+        <v>9.4200000000000433E-5</v>
       </c>
       <c r="E15" s="3">
         <f>D15*'Исходные данные'!D2</f>
-        <v>3.0144000000000134E-4</v>
+        <v>9.4200000000000433E-5</v>
       </c>
       <c r="F15" s="64" t="s">
         <v>107</v>
@@ -6880,7 +6880,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
       <c r="B16" s="18" t="s">
         <v>88</v>
@@ -6891,7 +6891,7 @@
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
     </row>
-    <row r="17" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="19" t="s">
         <v>164</v>
@@ -6902,7 +6902,7 @@
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
     </row>
-    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="41"/>
       <c r="B18" s="19" t="s">
         <v>104</v>
@@ -6913,7 +6913,7 @@
       <c r="F18" s="65"/>
       <c r="G18" s="68"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="41"/>
       <c r="B19" s="18" t="s">
         <v>87</v>
@@ -6924,7 +6924,7 @@
       <c r="F19" s="65"/>
       <c r="G19" s="68"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="19" t="s">
         <v>165</v>
@@ -6934,16 +6934,16 @@
       </c>
       <c r="D20" s="5">
         <f>0.02*D15</f>
-        <v>2.0096000000000091E-6</v>
+        <v>1.8840000000000088E-6</v>
       </c>
       <c r="E20" s="5">
         <f>D20*'Исходные данные'!D2</f>
-        <v>6.0288000000000277E-6</v>
+        <v>1.8840000000000088E-6</v>
       </c>
       <c r="F20" s="66"/>
       <c r="G20" s="69"/>
     </row>
-    <row r="21" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
         <v>2</v>
       </c>
@@ -6955,11 +6955,11 @@
       </c>
       <c r="D21" s="3">
         <f>(3.14*((('Исходные данные'!B4+2)/2)^2-(('Исходные данные'!B4-2)/2)^2))*0.15/1000</f>
-        <v>1.5072000000000067E-5</v>
+        <v>1.4130000000000065E-5</v>
       </c>
       <c r="E21" s="3">
         <f>D21*'Исходные данные'!D2</f>
-        <v>4.5216000000000199E-5</v>
+        <v>1.4130000000000065E-5</v>
       </c>
       <c r="F21" s="64" t="s">
         <v>94</v>
@@ -6968,7 +6968,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="18" t="s">
         <v>88</v>
@@ -6979,7 +6979,7 @@
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
     </row>
-    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="19" t="s">
         <v>92</v>
@@ -6990,7 +6990,7 @@
       <c r="F23" s="66"/>
       <c r="G23" s="69"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="16">
         <v>3</v>
       </c>
@@ -7002,18 +7002,18 @@
       </c>
       <c r="D24" s="3">
         <f>D21+D15</f>
-        <v>1.1555200000000051E-4</v>
+        <v>1.083300000000005E-4</v>
       </c>
       <c r="E24" s="3">
         <f>D24*'Исходные данные'!D2</f>
-        <v>3.466560000000015E-4</v>
+        <v>1.083300000000005E-4</v>
       </c>
       <c r="F24" s="64"/>
       <c r="G24" s="67" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="18" t="s">
         <v>88</v>
@@ -7024,7 +7024,7 @@
       <c r="F25" s="65"/>
       <c r="G25" s="68"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="19" t="s">
         <v>90</v>
@@ -7035,7 +7035,7 @@
       <c r="F26" s="66"/>
       <c r="G26" s="69"/>
     </row>
-    <row r="27" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <v>4</v>
       </c>
@@ -7047,11 +7047,11 @@
       </c>
       <c r="D27" s="3">
         <f>(3.14*((('Исходные данные'!B4+1)/2)^2-(('Исходные данные'!B4-1)/2)^2))*0.2</f>
-        <v>1.004800000000001E-2</v>
+        <v>9.4199999999999562E-3</v>
       </c>
       <c r="E27" s="3">
         <f>D27*'Исходные данные'!D2</f>
-        <v>3.0144000000000032E-2</v>
+        <v>9.4199999999999562E-3</v>
       </c>
       <c r="F27" s="64" t="s">
         <v>95</v>
@@ -7060,7 +7060,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="18" t="s">
         <v>87</v>
@@ -7071,7 +7071,7 @@
       <c r="F28" s="65"/>
       <c r="G28" s="68"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="17" t="s">
         <v>96</v>
@@ -7081,16 +7081,16 @@
       </c>
       <c r="D29" s="3">
         <f>D27*1.2</f>
-        <v>1.2057600000000012E-2</v>
+        <v>1.1303999999999948E-2</v>
       </c>
       <c r="E29" s="3">
         <f>D29*'Исходные данные'!D2</f>
-        <v>3.6172800000000033E-2</v>
+        <v>1.1303999999999948E-2</v>
       </c>
       <c r="F29" s="65"/>
       <c r="G29" s="68"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="17" t="s">
         <v>97</v>
@@ -7100,16 +7100,16 @@
       </c>
       <c r="D30" s="3">
         <f>D27*0.15</f>
-        <v>1.5072000000000015E-3</v>
+        <v>1.4129999999999935E-3</v>
       </c>
       <c r="E30" s="3">
         <f>D30*'Исходные данные'!D2</f>
-        <v>4.5216000000000041E-3</v>
+        <v>1.4129999999999935E-3</v>
       </c>
       <c r="F30" s="65"/>
       <c r="G30" s="68"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="18" t="s">
         <v>88</v>
@@ -7120,7 +7120,7 @@
       <c r="F31" s="65"/>
       <c r="G31" s="68"/>
     </row>
-    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="19" t="s">
         <v>98</v>
@@ -7131,7 +7131,7 @@
       <c r="F32" s="65"/>
       <c r="G32" s="68"/>
     </row>
-    <row r="33" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="19" t="s">
         <v>99</v>
@@ -7142,7 +7142,7 @@
       <c r="F33" s="65"/>
       <c r="G33" s="68"/>
     </row>
-    <row r="34" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="19" t="s">
         <v>100</v>
@@ -7153,7 +7153,7 @@
       <c r="F34" s="66"/>
       <c r="G34" s="69"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="16">
         <v>5</v>
       </c>
@@ -7165,11 +7165,11 @@
       </c>
       <c r="D35" s="3">
         <f>D27/100</f>
-        <v>1.004800000000001E-4</v>
+        <v>9.4199999999999566E-5</v>
       </c>
       <c r="E35" s="3">
         <f>D35*'Исходные данные'!D2</f>
-        <v>3.0144000000000026E-4</v>
+        <v>9.4199999999999566E-5</v>
       </c>
       <c r="F35" s="64" t="s">
         <v>107</v>
@@ -7178,7 +7178,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="18" t="s">
         <v>88</v>
@@ -7189,7 +7189,7 @@
       <c r="F36" s="65"/>
       <c r="G36" s="68"/>
     </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="17" t="s">
         <v>101</v>
@@ -7200,7 +7200,7 @@
       <c r="F37" s="66"/>
       <c r="G37" s="69"/>
     </row>
-    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="16">
         <v>6</v>
       </c>
@@ -7212,11 +7212,11 @@
       </c>
       <c r="D38" s="3">
         <f>(3.14*((('Исходные данные'!B4+1)/2)^2-(('Исходные данные'!B4-2)/2)^1))/1000</f>
-        <v>3.9252009599999999E-3</v>
+        <v>3.9251766250000004E-3</v>
       </c>
       <c r="E38" s="3">
         <f>D38*'Исходные данные'!D2</f>
-        <v>1.177560288E-2</v>
+        <v>3.9251766250000004E-3</v>
       </c>
       <c r="F38" s="64" t="s">
         <v>108</v>
@@ -7225,7 +7225,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="18" t="s">
         <v>87</v>
@@ -7236,7 +7236,7 @@
       <c r="F39" s="65"/>
       <c r="G39" s="68"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="17" t="s">
         <v>106</v>
@@ -7246,16 +7246,16 @@
       </c>
       <c r="D40" s="43">
         <f>0.00013*D38</f>
-        <v>5.1027612479999997E-7</v>
+        <v>5.1027296125000005E-7</v>
       </c>
       <c r="E40" s="43">
         <f>D40*'Исходные данные'!D2</f>
-        <v>1.5308283743999999E-6</v>
+        <v>5.1027296125000005E-7</v>
       </c>
       <c r="F40" s="65"/>
       <c r="G40" s="68"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="19" t="s">
         <v>59</v>
@@ -7265,16 +7265,16 @@
       </c>
       <c r="D41" s="3">
         <f>D38*100</f>
-        <v>0.39252009599999999</v>
+        <v>0.39251766250000003</v>
       </c>
       <c r="E41" s="3">
         <f>D41*'Исходные данные'!D2</f>
-        <v>1.177560288</v>
+        <v>0.39251766250000003</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
     </row>
-    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="18" t="s">
         <v>88</v>
@@ -7285,7 +7285,7 @@
       <c r="F42" s="65"/>
       <c r="G42" s="68"/>
     </row>
-    <row r="43" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="19" t="s">
         <v>104</v>
@@ -7296,7 +7296,7 @@
       <c r="F43" s="65"/>
       <c r="G43" s="68"/>
     </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="17" t="s">
         <v>105</v>
@@ -7307,7 +7307,7 @@
       <c r="F44" s="65"/>
       <c r="G44" s="68"/>
     </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="17" t="s">
         <v>90</v>
@@ -7318,7 +7318,7 @@
       <c r="F45" s="66"/>
       <c r="G45" s="69"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="16">
         <v>7</v>
       </c>
@@ -7330,11 +7330,11 @@
       </c>
       <c r="D46" s="3">
         <f>(3.14*((('Исходные данные'!B4+2)/2)^2-(('Исходные данные'!B4-2)/2)^2))*0.1</f>
-        <v>1.0048000000000045E-2</v>
+        <v>9.4200000000000447E-3</v>
       </c>
       <c r="E46" s="3">
         <f>D46*'Исходные данные'!D2</f>
-        <v>3.0144000000000136E-2</v>
+        <v>9.4200000000000447E-3</v>
       </c>
       <c r="F46" s="64" t="s">
         <v>107</v>
@@ -7343,7 +7343,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="18" t="s">
         <v>87</v>
@@ -7354,7 +7354,7 @@
       <c r="F47" s="65"/>
       <c r="G47" s="68"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="17" t="s">
         <v>110</v>
@@ -7364,16 +7364,16 @@
       </c>
       <c r="D48" s="3">
         <f>D46*1.3</f>
-        <v>1.3062400000000059E-2</v>
+        <v>1.2246000000000059E-2</v>
       </c>
       <c r="E48" s="3">
         <f>D48*'Исходные данные'!D2</f>
-        <v>3.9187200000000179E-2</v>
+        <v>1.2246000000000059E-2</v>
       </c>
       <c r="F48" s="65"/>
       <c r="G48" s="68"/>
     </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="17" t="s">
         <v>111</v>
@@ -7383,16 +7383,16 @@
       </c>
       <c r="D49" s="3">
         <f>D46*0.15</f>
-        <v>1.5072000000000067E-3</v>
+        <v>1.4130000000000067E-3</v>
       </c>
       <c r="E49" s="3">
         <f>D49*'Исходные данные'!D2</f>
-        <v>4.5216000000000197E-3</v>
+        <v>1.4130000000000067E-3</v>
       </c>
       <c r="F49" s="65"/>
       <c r="G49" s="68"/>
     </row>
-    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="18" t="s">
         <v>88</v>
@@ -7403,7 +7403,7 @@
       <c r="F50" s="65"/>
       <c r="G50" s="68"/>
     </row>
-    <row r="51" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="44" t="s">
         <v>98</v>
@@ -7414,7 +7414,7 @@
       <c r="F51" s="65"/>
       <c r="G51" s="68"/>
     </row>
-    <row r="52" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="44" t="s">
         <v>99</v>
@@ -7425,7 +7425,7 @@
       <c r="F52" s="65"/>
       <c r="G52" s="68"/>
     </row>
-    <row r="53" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
       <c r="B53" s="44" t="s">
         <v>100</v>
@@ -7436,7 +7436,7 @@
       <c r="F53" s="66"/>
       <c r="G53" s="69"/>
     </row>
-    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="16">
         <v>8</v>
       </c>
@@ -7448,11 +7448,11 @@
       </c>
       <c r="D54" s="3">
         <f>D46/100</f>
-        <v>1.0048000000000045E-4</v>
+        <v>9.4200000000000447E-5</v>
       </c>
       <c r="E54" s="3">
         <f>D54*'Исходные данные'!D2</f>
-        <v>3.0144000000000134E-4</v>
+        <v>9.4200000000000447E-5</v>
       </c>
       <c r="F54" s="64" t="s">
         <v>107</v>
@@ -7461,7 +7461,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="16"/>
       <c r="B55" s="18" t="s">
         <v>88</v>
@@ -7472,7 +7472,7 @@
       <c r="F55" s="65"/>
       <c r="G55" s="68"/>
     </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="17" t="s">
         <v>101</v>
@@ -7483,7 +7483,7 @@
       <c r="F56" s="66"/>
       <c r="G56" s="69"/>
     </row>
-    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="52" t="s">
         <v>120</v>
       </c>
@@ -7494,7 +7494,7 @@
       <c r="F57" s="53"/>
       <c r="G57" s="54"/>
     </row>
-    <row r="58" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A58" s="16">
         <v>1</v>
       </c>
@@ -7506,11 +7506,11 @@
       </c>
       <c r="D58" s="3">
         <f>(3.14*((('Исходные данные'!B4+1)/2)^2-(('Исходные данные'!B4-1)/2)^2))*0.5/10</f>
-        <v>2.5120000000000025E-3</v>
+        <v>2.354999999999989E-3</v>
       </c>
       <c r="E58" s="3">
         <f>D58*'Исходные данные'!D2</f>
-        <v>7.536000000000008E-3</v>
+        <v>2.354999999999989E-3</v>
       </c>
       <c r="F58" s="64" t="s">
         <v>47</v>
@@ -7519,7 +7519,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="18" t="s">
         <v>87</v>
@@ -7530,7 +7530,7 @@
       <c r="F59" s="65"/>
       <c r="G59" s="68"/>
     </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="19" t="s">
         <v>59</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="D60" s="3">
         <f>2.5*D58</f>
-        <v>6.2800000000000061E-3</v>
+        <v>5.8874999999999726E-3</v>
       </c>
       <c r="E60" s="3">
         <f>D60*'Исходные данные'!$D$2</f>
-        <v>1.8840000000000016E-2</v>
+        <v>5.8874999999999726E-3</v>
       </c>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
     </row>
-    <row r="61" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A61" s="16"/>
       <c r="B61" s="19" t="s">
         <v>49</v>
@@ -7559,16 +7559,16 @@
       </c>
       <c r="D61" s="3">
         <f>0.0115*D58</f>
-        <v>2.8888000000000029E-5</v>
+        <v>2.7082499999999875E-5</v>
       </c>
       <c r="E61" s="3">
         <f>D61*'Исходные данные'!$D$2</f>
-        <v>8.666400000000009E-5</v>
+        <v>2.7082499999999875E-5</v>
       </c>
       <c r="F61" s="65"/>
       <c r="G61" s="68"/>
     </row>
-    <row r="62" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A62" s="16"/>
       <c r="B62" s="19" t="s">
         <v>50</v>
@@ -7578,16 +7578,16 @@
       </c>
       <c r="D62" s="3">
         <f>0.095*D58</f>
-        <v>2.3864000000000025E-4</v>
+        <v>2.2372499999999897E-4</v>
       </c>
       <c r="E62" s="3">
         <f>D62*'Исходные данные'!$D$2</f>
-        <v>7.1592000000000075E-4</v>
+        <v>2.2372499999999897E-4</v>
       </c>
       <c r="F62" s="65"/>
       <c r="G62" s="68"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="16"/>
       <c r="B63" s="17" t="s">
         <v>56</v>
@@ -7597,16 +7597,16 @@
       </c>
       <c r="D63" s="3">
         <f>D58*10.5</f>
-        <v>2.6376000000000028E-2</v>
+        <v>2.4727499999999885E-2</v>
       </c>
       <c r="E63" s="3">
         <f>D63*'Исходные данные'!$D$2</f>
-        <v>7.9128000000000087E-2</v>
+        <v>2.4727499999999885E-2</v>
       </c>
       <c r="F63" s="65"/>
       <c r="G63" s="68"/>
     </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="16"/>
       <c r="B64" s="17" t="s">
         <v>57</v>
@@ -7616,16 +7616,16 @@
       </c>
       <c r="D64" s="3">
         <f>3.14*('Исходные данные'!B4+1)*2.11</f>
-        <v>6.7314064</v>
+        <v>6.7247809999999983</v>
       </c>
       <c r="E64" s="3">
         <f>D64*'Исходные данные'!$D$2</f>
-        <v>20.194219199999999</v>
+        <v>6.7247809999999983</v>
       </c>
       <c r="F64" s="65"/>
       <c r="G64" s="68"/>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="16"/>
       <c r="B65" s="18" t="s">
         <v>88</v>
@@ -7636,7 +7636,7 @@
       <c r="F65" s="65"/>
       <c r="G65" s="68"/>
     </row>
-    <row r="66" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="19" t="s">
         <v>113</v>
@@ -7647,7 +7647,7 @@
       <c r="F66" s="65"/>
       <c r="G66" s="68"/>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="16"/>
       <c r="B67" s="17" t="s">
         <v>114</v>
@@ -7658,7 +7658,7 @@
       <c r="F67" s="65"/>
       <c r="G67" s="68"/>
     </row>
-    <row r="68" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A68" s="16"/>
       <c r="B68" s="19" t="s">
         <v>115</v>
@@ -7669,7 +7669,7 @@
       <c r="F68" s="65"/>
       <c r="G68" s="68"/>
     </row>
-    <row r="69" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A69" s="16"/>
       <c r="B69" s="19" t="s">
         <v>116</v>
@@ -7680,7 +7680,7 @@
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
     </row>
-    <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A70" s="16"/>
       <c r="B70" s="19" t="s">
         <v>100</v>
@@ -7691,7 +7691,7 @@
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="16"/>
       <c r="B71" s="19" t="s">
         <v>90</v>
@@ -7702,7 +7702,7 @@
       <c r="F71" s="65"/>
       <c r="G71" s="68"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="16"/>
       <c r="B72" s="17" t="s">
         <v>117</v>
@@ -7713,7 +7713,7 @@
       <c r="F72" s="66"/>
       <c r="G72" s="69"/>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="52" t="s">
         <v>121</v>
       </c>
@@ -7724,7 +7724,7 @@
       <c r="F73" s="53"/>
       <c r="G73" s="54"/>
     </row>
-    <row r="74" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="16">
         <v>1</v>
       </c>
@@ -7736,18 +7736,18 @@
       </c>
       <c r="D74" s="3">
         <f>'Исходные данные'!H11</f>
-        <v>1378.64</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="E74" s="3">
         <f>D74*'Исходные данные'!$D$2</f>
-        <v>4135.92</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="F74" s="64" t="s">
         <v>19</v>
       </c>
       <c r="G74" s="67"/>
     </row>
-    <row r="75" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="16"/>
       <c r="B75" s="18" t="s">
         <v>87</v>
@@ -7758,7 +7758,7 @@
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
       <c r="B76" s="19" t="s">
         <v>16</v>
@@ -7768,16 +7768,16 @@
       </c>
       <c r="D76" s="3">
         <f>D74</f>
-        <v>1378.64</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="E76" s="3">
         <f>D76*'Исходные данные'!$D$2</f>
-        <v>4135.92</v>
+        <v>1.3786400000000001</v>
       </c>
       <c r="F76" s="65"/>
       <c r="G76" s="68"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="16"/>
       <c r="B77" s="18" t="s">
         <v>88</v>
@@ -7788,7 +7788,7 @@
       <c r="F77" s="65"/>
       <c r="G77" s="68"/>
     </row>
-    <row r="78" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A78" s="16"/>
       <c r="B78" s="19" t="s">
         <v>113</v>
@@ -7799,7 +7799,7 @@
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
     </row>
-    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="16"/>
       <c r="B79" s="21" t="s">
         <v>144</v>
@@ -7810,7 +7810,7 @@
       <c r="F79" s="65"/>
       <c r="G79" s="68"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="16"/>
       <c r="B80" s="17" t="s">
         <v>90</v>
@@ -7821,7 +7821,7 @@
       <c r="F80" s="65"/>
       <c r="G80" s="68"/>
     </row>
-    <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="16"/>
       <c r="B81" s="17" t="s">
         <v>134</v>
@@ -7832,7 +7832,7 @@
       <c r="F81" s="65"/>
       <c r="G81" s="68"/>
     </row>
-    <row r="82" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="16">
         <v>2</v>
       </c>
@@ -7844,16 +7844,16 @@
       </c>
       <c r="D82" s="3">
         <f>'Исходные данные'!H12</f>
-        <v>9244.64</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="E82" s="3">
         <f>D82*'Исходные данные'!$D$2</f>
-        <v>27733.919999999998</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
     </row>
-    <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="16"/>
       <c r="B83" s="18" t="s">
         <v>87</v>
@@ -7864,7 +7864,7 @@
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
     </row>
-    <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="16"/>
       <c r="B84" s="19" t="s">
         <v>16</v>
@@ -7874,16 +7874,16 @@
       </c>
       <c r="D84" s="3">
         <f>D82</f>
-        <v>9244.64</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="E84" s="3">
         <f>D84*'Исходные данные'!$D$2</f>
-        <v>27733.919999999998</v>
+        <v>9.2446399999999986</v>
       </c>
       <c r="F84" s="65"/>
       <c r="G84" s="68"/>
     </row>
-    <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="16"/>
       <c r="B85" s="18" t="s">
         <v>88</v>
@@ -7894,7 +7894,7 @@
       <c r="F85" s="65"/>
       <c r="G85" s="68"/>
     </row>
-    <row r="86" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A86" s="16"/>
       <c r="B86" s="19" t="s">
         <v>113</v>
@@ -7905,7 +7905,7 @@
       <c r="F86" s="65"/>
       <c r="G86" s="68"/>
     </row>
-    <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="16"/>
       <c r="B87" s="19" t="s">
         <v>144</v>
@@ -7916,7 +7916,7 @@
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
     </row>
-    <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="16"/>
       <c r="B88" s="17" t="s">
         <v>90</v>
@@ -7927,7 +7927,7 @@
       <c r="F88" s="65"/>
       <c r="G88" s="68"/>
     </row>
-    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="16"/>
       <c r="B89" s="17" t="s">
         <v>134</v>
@@ -7938,7 +7938,7 @@
       <c r="F89" s="65"/>
       <c r="G89" s="68"/>
     </row>
-    <row r="90" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A90" s="16">
         <v>3</v>
       </c>
@@ -7950,16 +7950,16 @@
       </c>
       <c r="D90" s="3">
         <f>'Исходные данные'!H13</f>
-        <v>1834.64</v>
+        <v>1.83464</v>
       </c>
       <c r="E90" s="3">
         <f>D90*'Исходные данные'!$D$2</f>
-        <v>5503.92</v>
+        <v>1.83464</v>
       </c>
       <c r="F90" s="65"/>
       <c r="G90" s="68"/>
     </row>
-    <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="16"/>
       <c r="B91" s="18" t="s">
         <v>87</v>
@@ -7970,7 +7970,7 @@
       <c r="F91" s="65"/>
       <c r="G91" s="68"/>
     </row>
-    <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="16"/>
       <c r="B92" s="19" t="s">
         <v>16</v>
@@ -7980,16 +7980,16 @@
       </c>
       <c r="D92" s="3">
         <f>D90</f>
-        <v>1834.64</v>
+        <v>1.83464</v>
       </c>
       <c r="E92" s="3">
         <f>D92*'Исходные данные'!$D$2</f>
-        <v>5503.92</v>
+        <v>1.83464</v>
       </c>
       <c r="F92" s="65"/>
       <c r="G92" s="68"/>
     </row>
-    <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="16"/>
       <c r="B93" s="18" t="s">
         <v>88</v>
@@ -8000,7 +8000,7 @@
       <c r="F93" s="65"/>
       <c r="G93" s="68"/>
     </row>
-    <row r="94" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A94" s="16"/>
       <c r="B94" s="19" t="s">
         <v>113</v>
@@ -8011,7 +8011,7 @@
       <c r="F94" s="65"/>
       <c r="G94" s="68"/>
     </row>
-    <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="16"/>
       <c r="B95" s="19" t="s">
         <v>144</v>
@@ -8022,7 +8022,7 @@
       <c r="F95" s="65"/>
       <c r="G95" s="68"/>
     </row>
-    <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="16"/>
       <c r="B96" s="17" t="s">
         <v>90</v>
@@ -8033,7 +8033,7 @@
       <c r="F96" s="65"/>
       <c r="G96" s="68"/>
     </row>
-    <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="16"/>
       <c r="B97" s="17" t="s">
         <v>134</v>
@@ -8044,7 +8044,7 @@
       <c r="F97" s="65"/>
       <c r="G97" s="68"/>
     </row>
-    <row r="98" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="16">
         <v>4</v>
       </c>
@@ -8056,16 +8056,16 @@
       </c>
       <c r="D98" s="3">
         <f>'Исходные данные'!H14</f>
-        <v>2260.2399999999998</v>
+        <v>2.26024</v>
       </c>
       <c r="E98" s="3">
         <f>D98*'Исходные данные'!$D$2</f>
-        <v>6780.7199999999993</v>
+        <v>2.26024</v>
       </c>
       <c r="F98" s="65"/>
       <c r="G98" s="68"/>
     </row>
-    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="16"/>
       <c r="B99" s="18" t="s">
         <v>87</v>
@@ -8076,7 +8076,7 @@
       <c r="F99" s="65"/>
       <c r="G99" s="68"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="16"/>
       <c r="B100" s="19" t="s">
         <v>16</v>
@@ -8086,16 +8086,16 @@
       </c>
       <c r="D100" s="3">
         <f>D98</f>
-        <v>2260.2399999999998</v>
+        <v>2.26024</v>
       </c>
       <c r="E100" s="3">
         <f>D100*'Исходные данные'!$D$2</f>
-        <v>6780.7199999999993</v>
+        <v>2.26024</v>
       </c>
       <c r="F100" s="65"/>
       <c r="G100" s="68"/>
     </row>
-    <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="16"/>
       <c r="B101" s="18" t="s">
         <v>88</v>
@@ -8106,7 +8106,7 @@
       <c r="F101" s="65"/>
       <c r="G101" s="68"/>
     </row>
-    <row r="102" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A102" s="16"/>
       <c r="B102" s="19" t="s">
         <v>113</v>
@@ -8117,7 +8117,7 @@
       <c r="F102" s="65"/>
       <c r="G102" s="68"/>
     </row>
-    <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="16"/>
       <c r="B103" s="19" t="s">
         <v>144</v>
@@ -8128,7 +8128,7 @@
       <c r="F103" s="65"/>
       <c r="G103" s="68"/>
     </row>
-    <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="16"/>
       <c r="B104" s="17" t="s">
         <v>90</v>
@@ -8139,7 +8139,7 @@
       <c r="F104" s="65"/>
       <c r="G104" s="68"/>
     </row>
-    <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="16"/>
       <c r="B105" s="17" t="s">
         <v>134</v>
@@ -8150,7 +8150,7 @@
       <c r="F105" s="65"/>
       <c r="G105" s="68"/>
     </row>
-    <row r="106" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A106" s="16">
         <v>5</v>
       </c>
@@ -8162,16 +8162,16 @@
       </c>
       <c r="D106" s="3">
         <f>'Исходные данные'!H15</f>
-        <v>481.84</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="E106" s="3">
         <f>D106*'Исходные данные'!$D$2</f>
-        <v>1445.52</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="F106" s="65"/>
       <c r="G106" s="68"/>
     </row>
-    <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="16"/>
       <c r="B107" s="18" t="s">
         <v>87</v>
@@ -8182,7 +8182,7 @@
       <c r="F107" s="65"/>
       <c r="G107" s="68"/>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="16"/>
       <c r="B108" s="19" t="s">
         <v>16</v>
@@ -8192,16 +8192,16 @@
       </c>
       <c r="D108" s="3">
         <f>D106</f>
-        <v>481.84</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="E108" s="3">
         <f>D108*'Исходные данные'!$D$2</f>
-        <v>1445.52</v>
+        <v>0.48183999999999994</v>
       </c>
       <c r="F108" s="65"/>
       <c r="G108" s="68"/>
     </row>
-    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="16"/>
       <c r="B109" s="18" t="s">
         <v>88</v>
@@ -8212,7 +8212,7 @@
       <c r="F109" s="65"/>
       <c r="G109" s="68"/>
     </row>
-    <row r="110" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A110" s="16"/>
       <c r="B110" s="19" t="s">
         <v>113</v>
@@ -8223,7 +8223,7 @@
       <c r="F110" s="65"/>
       <c r="G110" s="68"/>
     </row>
-    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="16"/>
       <c r="B111" s="19" t="s">
         <v>144</v>
@@ -8234,7 +8234,7 @@
       <c r="F111" s="65"/>
       <c r="G111" s="68"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="16"/>
       <c r="B112" s="17" t="s">
         <v>90</v>
@@ -8245,7 +8245,7 @@
       <c r="F112" s="65"/>
       <c r="G112" s="68"/>
     </row>
-    <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="16"/>
       <c r="B113" s="17" t="s">
         <v>134</v>
@@ -8256,7 +8256,7 @@
       <c r="F113" s="66"/>
       <c r="G113" s="69"/>
     </row>
-    <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="16">
         <v>6</v>
       </c>
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D114" s="3">
         <f>'Исходные данные'!D16/100</f>
-        <v>136733.258168</v>
+        <v>136.73325816799999</v>
       </c>
       <c r="E114" s="3">
         <f>D114*'Исходные данные'!$D$2</f>
-        <v>410199.77450399997</v>
+        <v>136.73325816799999</v>
       </c>
       <c r="F114" s="64" t="s">
         <v>19</v>
@@ -8281,7 +8281,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="16"/>
       <c r="B115" s="18" t="s">
         <v>87</v>
@@ -8292,7 +8292,7 @@
       <c r="F115" s="65"/>
       <c r="G115" s="68"/>
     </row>
-    <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="16"/>
       <c r="B116" s="19" t="s">
         <v>126</v>
@@ -8302,16 +8302,16 @@
       </c>
       <c r="D116" s="3">
         <f>'Исходные данные'!H16</f>
-        <v>1068.56</v>
+        <v>1.06856</v>
       </c>
       <c r="E116" s="3">
         <f>D116*'Исходные данные'!$D$2</f>
-        <v>3205.68</v>
+        <v>1.06856</v>
       </c>
       <c r="F116" s="65"/>
       <c r="G116" s="68"/>
     </row>
-    <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="16"/>
       <c r="B117" s="18" t="s">
         <v>88</v>
@@ -8322,7 +8322,7 @@
       <c r="F117" s="65"/>
       <c r="G117" s="68"/>
     </row>
-    <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="16"/>
       <c r="B118" s="19" t="s">
         <v>90</v>
@@ -8333,7 +8333,7 @@
       <c r="F118" s="66"/>
       <c r="G118" s="69"/>
     </row>
-    <row r="119" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A119" s="70" t="s">
         <v>28</v>
       </c>
@@ -8343,16 +8343,16 @@
       </c>
       <c r="D119" s="3">
         <f>D74+D82+D90+D98+D106</f>
-        <v>15199.999999999998</v>
+        <v>15.2</v>
       </c>
       <c r="E119" s="3">
         <f>D119*'Исходные данные'!$D$2</f>
-        <v>45599.999999999993</v>
+        <v>15.2</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="20"/>
     </row>
-    <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="70" t="s">
         <v>128</v>
       </c>
@@ -8362,16 +8362,16 @@
       </c>
       <c r="D120" s="3">
         <f>D116</f>
-        <v>1068.56</v>
+        <v>1.06856</v>
       </c>
       <c r="E120" s="3">
         <f>D120*'Исходные данные'!$D$2</f>
-        <v>3205.68</v>
+        <v>1.06856</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="20"/>
     </row>
-    <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="70" t="s">
         <v>129</v>
       </c>
@@ -8381,16 +8381,16 @@
       </c>
       <c r="D121" s="3">
         <f>D119+D120</f>
-        <v>16268.559999999998</v>
+        <v>16.268560000000001</v>
       </c>
       <c r="E121" s="3">
         <f>D121*'Исходные данные'!$D$2</f>
-        <v>48805.679999999993</v>
+        <v>16.268560000000001</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="20"/>
     </row>
-    <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="52" t="s">
         <v>67</v>
       </c>
@@ -8401,7 +8401,7 @@
       <c r="F122" s="53"/>
       <c r="G122" s="54"/>
     </row>
-    <row r="123" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A123" s="16">
         <v>1</v>
       </c>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="E123" s="3">
         <f>D123*'Исходные данные'!$D$2</f>
-        <v>-3.78E-2</v>
+        <v>-1.26E-2</v>
       </c>
       <c r="F123" s="64" t="s">
         <v>19</v>
       </c>
       <c r="G123" s="67"/>
     </row>
-    <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="16"/>
       <c r="B124" s="18" t="s">
         <v>87</v>
@@ -8435,7 +8435,7 @@
       <c r="F124" s="65"/>
       <c r="G124" s="68"/>
     </row>
-    <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="16"/>
       <c r="B125" s="19" t="s">
         <v>16</v>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E125" s="3">
         <f>D125*'Исходные данные'!$D$2</f>
-        <v>-3.78E-2</v>
+        <v>-1.26E-2</v>
       </c>
       <c r="F125" s="65"/>
       <c r="G125" s="68"/>
     </row>
-    <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="16"/>
       <c r="B126" s="18" t="s">
         <v>88</v>
@@ -8465,7 +8465,7 @@
       <c r="F126" s="65"/>
       <c r="G126" s="68"/>
     </row>
-    <row r="127" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A127" s="16"/>
       <c r="B127" s="19" t="s">
         <v>113</v>
@@ -8476,7 +8476,7 @@
       <c r="F127" s="65"/>
       <c r="G127" s="68"/>
     </row>
-    <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="16"/>
       <c r="B128" s="19" t="s">
         <v>144</v>
@@ -8487,7 +8487,7 @@
       <c r="F128" s="65"/>
       <c r="G128" s="68"/>
     </row>
-    <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="16"/>
       <c r="B129" s="17" t="s">
         <v>90</v>
@@ -8498,7 +8498,7 @@
       <c r="F129" s="65"/>
       <c r="G129" s="68"/>
     </row>
-    <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="16"/>
       <c r="B130" s="17" t="s">
         <v>134</v>
@@ -8509,7 +8509,7 @@
       <c r="F130" s="66"/>
       <c r="G130" s="69"/>
     </row>
-    <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="16">
         <v>2</v>
       </c>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="E131" s="1">
         <f>D131*'Исходные данные'!$D$2</f>
-        <v>-90</v>
+        <v>-30</v>
       </c>
       <c r="F131" s="73"/>
       <c r="G131" s="67"/>
     </row>
-    <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="16"/>
       <c r="B132" s="18" t="s">
         <v>87</v>
@@ -8541,7 +8541,7 @@
       <c r="F132" s="74"/>
       <c r="G132" s="68"/>
     </row>
-    <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="16"/>
       <c r="B133" s="17" t="s">
         <v>35</v>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="E133" s="4">
         <f>D133*'Исходные данные'!$D$2</f>
-        <v>-90</v>
+        <v>-30</v>
       </c>
       <c r="F133" s="74"/>
       <c r="G133" s="68"/>
     </row>
-    <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="16"/>
       <c r="B134" s="18" t="s">
         <v>88</v>
@@ -8571,7 +8571,7 @@
       <c r="F134" s="74"/>
       <c r="G134" s="68"/>
     </row>
-    <row r="135" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A135" s="16"/>
       <c r="B135" s="19" t="s">
         <v>113</v>
@@ -8582,7 +8582,7 @@
       <c r="F135" s="74"/>
       <c r="G135" s="68"/>
     </row>
-    <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="16"/>
       <c r="B136" s="19" t="s">
         <v>144</v>
@@ -8593,7 +8593,7 @@
       <c r="F136" s="74"/>
       <c r="G136" s="68"/>
     </row>
-    <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="16"/>
       <c r="B137" s="17" t="s">
         <v>90</v>
@@ -8604,7 +8604,7 @@
       <c r="F137" s="74"/>
       <c r="G137" s="68"/>
     </row>
-    <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="16"/>
       <c r="B138" s="17" t="s">
         <v>134</v>
@@ -8615,7 +8615,7 @@
       <c r="F138" s="75"/>
       <c r="G138" s="69"/>
     </row>
-    <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="16">
         <v>3</v>
       </c>
@@ -8631,12 +8631,12 @@
       </c>
       <c r="E139" s="4">
         <f>D139*'Исходные данные'!$D$2</f>
-        <v>-5.3693999999999999E-3</v>
+        <v>-1.7898E-3</v>
       </c>
       <c r="F139" s="64"/>
       <c r="G139" s="67"/>
     </row>
-    <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="16"/>
       <c r="B140" s="18" t="s">
         <v>87</v>
@@ -8647,7 +8647,7 @@
       <c r="F140" s="65"/>
       <c r="G140" s="68"/>
     </row>
-    <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="16"/>
       <c r="B141" s="1" t="s">
         <v>74</v>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="E141" s="1">
         <f>D141*'Исходные данные'!$D$2</f>
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="F141" s="65"/>
       <c r="G141" s="68"/>
     </row>
-    <row r="142" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="16"/>
       <c r="B142" s="18" t="s">
         <v>88</v>
@@ -8677,7 +8677,7 @@
       <c r="F142" s="65"/>
       <c r="G142" s="68"/>
     </row>
-    <row r="143" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A143" s="16"/>
       <c r="B143" s="19" t="s">
         <v>113</v>
@@ -8688,7 +8688,7 @@
       <c r="F143" s="65"/>
       <c r="G143" s="68"/>
     </row>
-    <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="16"/>
       <c r="B144" s="19" t="s">
         <v>144</v>
@@ -8699,7 +8699,7 @@
       <c r="F144" s="65"/>
       <c r="G144" s="68"/>
     </row>
-    <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="16"/>
       <c r="B145" s="17" t="s">
         <v>90</v>
@@ -8710,7 +8710,7 @@
       <c r="F145" s="65"/>
       <c r="G145" s="68"/>
     </row>
-    <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="16"/>
       <c r="B146" s="17" t="s">
         <v>134</v>
@@ -8721,7 +8721,7 @@
       <c r="F146" s="66"/>
       <c r="G146" s="69"/>
     </row>
-    <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="16">
         <v>4</v>
       </c>
@@ -8733,16 +8733,16 @@
       </c>
       <c r="D147" s="4">
         <f>('Исходные данные'!D9*('Исходные данные'!B5+2*'Исходные данные'!C3-2.5+0.4))/100</f>
-        <v>0.30614999999999998</v>
+        <v>0.30705000000000005</v>
       </c>
       <c r="E147" s="4">
         <f>D147*'Исходные данные'!$D$2</f>
-        <v>0.91844999999999999</v>
+        <v>0.30705000000000005</v>
       </c>
       <c r="F147" s="64"/>
       <c r="G147" s="67"/>
     </row>
-    <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="16"/>
       <c r="B148" s="18" t="s">
         <v>87</v>
@@ -8753,7 +8753,7 @@
       <c r="F148" s="65"/>
       <c r="G148" s="68"/>
     </row>
-    <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="16"/>
       <c r="B149" s="1" t="s">
         <v>74</v>
@@ -8767,12 +8767,12 @@
       </c>
       <c r="E149" s="1">
         <f>D149*'Исходные данные'!$D$2</f>
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="F149" s="65"/>
       <c r="G149" s="68"/>
     </row>
-    <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="16"/>
       <c r="B150" s="18" t="s">
         <v>88</v>
@@ -8783,7 +8783,7 @@
       <c r="F150" s="65"/>
       <c r="G150" s="68"/>
     </row>
-    <row r="151" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A151" s="16"/>
       <c r="B151" s="19" t="s">
         <v>113</v>
@@ -8794,7 +8794,7 @@
       <c r="F151" s="65"/>
       <c r="G151" s="68"/>
     </row>
-    <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="16"/>
       <c r="B152" s="19" t="s">
         <v>144</v>
@@ -8805,7 +8805,7 @@
       <c r="F152" s="65"/>
       <c r="G152" s="68"/>
     </row>
-    <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="16"/>
       <c r="B153" s="17" t="s">
         <v>90</v>
@@ -8816,7 +8816,7 @@
       <c r="F153" s="65"/>
       <c r="G153" s="68"/>
     </row>
-    <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="16"/>
       <c r="B154" s="17" t="s">
         <v>134</v>
@@ -8827,7 +8827,7 @@
       <c r="F154" s="66"/>
       <c r="G154" s="69"/>
     </row>
-    <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="16">
         <v>5</v>
       </c>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="E155" s="1">
         <f>D155*'Исходные данные'!$D$2</f>
-        <v>-57</v>
+        <v>-19</v>
       </c>
       <c r="F155" s="76"/>
       <c r="G155" s="72"/>
     </row>
-    <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="16"/>
       <c r="B156" s="18" t="s">
         <v>87</v>
@@ -8859,7 +8859,7 @@
       <c r="F156" s="76"/>
       <c r="G156" s="72"/>
     </row>
-    <row r="157" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="16"/>
       <c r="B157" s="17" t="s">
         <v>38</v>
@@ -8873,12 +8873,12 @@
       </c>
       <c r="E157" s="1">
         <f>D157*'Исходные данные'!$D$2</f>
-        <v>-57</v>
+        <v>-19</v>
       </c>
       <c r="F157" s="76"/>
       <c r="G157" s="72"/>
     </row>
-    <row r="158" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="16"/>
       <c r="B158" s="18" t="s">
         <v>88</v>
@@ -8889,7 +8889,7 @@
       <c r="F158" s="76"/>
       <c r="G158" s="72"/>
     </row>
-    <row r="159" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="16"/>
       <c r="B159" s="19" t="s">
         <v>113</v>
@@ -8900,7 +8900,7 @@
       <c r="F159" s="76"/>
       <c r="G159" s="72"/>
     </row>
-    <row r="160" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="16"/>
       <c r="B160" s="19" t="s">
         <v>144</v>
@@ -8911,7 +8911,7 @@
       <c r="F160" s="76"/>
       <c r="G160" s="72"/>
     </row>
-    <row r="161" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="16"/>
       <c r="B161" s="17" t="s">
         <v>90</v>
@@ -8922,7 +8922,7 @@
       <c r="F161" s="76"/>
       <c r="G161" s="72"/>
     </row>
-    <row r="162" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="16"/>
       <c r="B162" s="17" t="s">
         <v>134</v>
@@ -8933,7 +8933,7 @@
       <c r="F162" s="76"/>
       <c r="G162" s="72"/>
     </row>
-    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="52" t="s">
         <v>70</v>
       </c>
@@ -8944,7 +8944,7 @@
       <c r="F163" s="53"/>
       <c r="G163" s="54"/>
     </row>
-    <row r="164" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="16">
         <v>1</v>
       </c>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="E164" s="1">
         <f>D164*'Исходные данные'!$D$2</f>
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F164" s="64" t="s">
         <v>19</v>
       </c>
       <c r="G164" s="67"/>
     </row>
-    <row r="165" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="16"/>
       <c r="B165" s="18" t="s">
         <v>87</v>
@@ -8978,7 +8978,7 @@
       <c r="F165" s="65"/>
       <c r="G165" s="68"/>
     </row>
-    <row r="166" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="16"/>
       <c r="B166" s="19" t="s">
         <v>16</v>
@@ -8992,12 +8992,12 @@
       </c>
       <c r="E166" s="1">
         <f>D166*'Исходные данные'!$D$2</f>
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F166" s="65"/>
       <c r="G166" s="68"/>
     </row>
-    <row r="167" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="16"/>
       <c r="B167" s="18" t="s">
         <v>88</v>
@@ -9008,7 +9008,7 @@
       <c r="F167" s="65"/>
       <c r="G167" s="68"/>
     </row>
-    <row r="168" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="16"/>
       <c r="B168" s="19" t="s">
         <v>113</v>
@@ -9019,7 +9019,7 @@
       <c r="F168" s="65"/>
       <c r="G168" s="68"/>
     </row>
-    <row r="169" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="16"/>
       <c r="B169" s="17" t="s">
         <v>90</v>
@@ -9030,7 +9030,7 @@
       <c r="F169" s="65"/>
       <c r="G169" s="68"/>
     </row>
-    <row r="170" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="16"/>
       <c r="B170" s="17" t="s">
         <v>134</v>
@@ -9041,7 +9041,7 @@
       <c r="F170" s="66"/>
       <c r="G170" s="69"/>
     </row>
-    <row r="171" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="16">
         <v>2</v>
       </c>
@@ -9056,12 +9056,12 @@
       </c>
       <c r="E171" s="1">
         <f>D171*'Исходные данные'!$D$2</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F171" s="64"/>
       <c r="G171" s="67"/>
     </row>
-    <row r="172" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="16"/>
       <c r="B172" s="18" t="s">
         <v>87</v>
@@ -9072,7 +9072,7 @@
       <c r="F172" s="65"/>
       <c r="G172" s="68"/>
     </row>
-    <row r="173" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="16"/>
       <c r="B173" s="17" t="s">
         <v>136</v>
@@ -9085,12 +9085,12 @@
       </c>
       <c r="E173" s="1">
         <f>D173*'Исходные данные'!$D$2</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F173" s="66"/>
       <c r="G173" s="69"/>
     </row>
-    <row r="174" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="16">
         <v>3</v>
       </c>
@@ -9105,12 +9105,12 @@
       </c>
       <c r="E174" s="1">
         <f>D174*'Исходные данные'!$D$2</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F174" s="64"/>
       <c r="G174" s="67"/>
     </row>
-    <row r="175" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="16"/>
       <c r="B175" s="18" t="s">
         <v>87</v>
@@ -9121,7 +9121,7 @@
       <c r="F175" s="65"/>
       <c r="G175" s="68"/>
     </row>
-    <row r="176" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="16"/>
       <c r="B176" s="17" t="s">
         <v>39</v>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="E176" s="1">
         <f>D176*'Исходные данные'!$D$2</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F176" s="66"/>
       <c r="G176" s="69"/>
     </row>
-    <row r="177" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="52" t="s">
         <v>32</v>
       </c>
@@ -9150,7 +9150,7 @@
       <c r="F177" s="53"/>
       <c r="G177" s="54"/>
     </row>
-    <row r="178" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A178" s="16">
         <v>1</v>
       </c>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="G178" s="67"/>
     </row>
-    <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="16"/>
       <c r="B179" s="18" t="s">
         <v>87</v>
@@ -9184,7 +9184,7 @@
       <c r="F179" s="65"/>
       <c r="G179" s="68"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="16"/>
       <c r="B180" s="2" t="s">
         <v>16</v>
@@ -9203,7 +9203,7 @@
       <c r="F180" s="65"/>
       <c r="G180" s="68"/>
     </row>
-    <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="16"/>
       <c r="B181" s="18" t="s">
         <v>88</v>
@@ -9214,7 +9214,7 @@
       <c r="F181" s="65"/>
       <c r="G181" s="68"/>
     </row>
-    <row r="182" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A182" s="16"/>
       <c r="B182" s="19" t="s">
         <v>113</v>
@@ -9225,7 +9225,7 @@
       <c r="F182" s="65"/>
       <c r="G182" s="68"/>
     </row>
-    <row r="183" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="16"/>
       <c r="B183" s="19" t="s">
         <v>144</v>
@@ -9236,7 +9236,7 @@
       <c r="F183" s="65"/>
       <c r="G183" s="68"/>
     </row>
-    <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="16"/>
       <c r="B184" s="17" t="s">
         <v>90</v>
@@ -9247,7 +9247,7 @@
       <c r="F184" s="65"/>
       <c r="G184" s="68"/>
     </row>
-    <row r="185" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="16"/>
       <c r="B185" s="17" t="s">
         <v>134</v>
@@ -9258,7 +9258,7 @@
       <c r="F185" s="66"/>
       <c r="G185" s="69"/>
     </row>
-    <row r="186" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="16">
         <v>2</v>
       </c>
@@ -9274,14 +9274,14 @@
       </c>
       <c r="E186" s="3">
         <f>D186*'Исходные данные'!$D$2</f>
-        <v>2.9209800000000001E-2</v>
+        <v>9.7365999999999998E-3</v>
       </c>
       <c r="F186" s="64"/>
       <c r="G186" s="67" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="16"/>
       <c r="B187" s="18" t="s">
         <v>87</v>
@@ -9292,7 +9292,7 @@
       <c r="F187" s="65"/>
       <c r="G187" s="68"/>
     </row>
-    <row r="188" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="16"/>
       <c r="B188" s="19" t="s">
         <v>75</v>
@@ -9305,12 +9305,12 @@
       </c>
       <c r="E188" s="4">
         <f>D188*'Исходные данные'!$D$2</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F188" s="65"/>
       <c r="G188" s="68"/>
     </row>
-    <row r="189" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="16"/>
       <c r="B189" s="18" t="s">
         <v>88</v>
@@ -9321,7 +9321,7 @@
       <c r="F189" s="65"/>
       <c r="G189" s="68"/>
     </row>
-    <row r="190" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A190" s="16"/>
       <c r="B190" s="19" t="s">
         <v>141</v>
@@ -9332,7 +9332,7 @@
       <c r="F190" s="65"/>
       <c r="G190" s="68"/>
     </row>
-    <row r="191" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="16"/>
       <c r="B191" s="19" t="s">
         <v>142</v>
@@ -9343,7 +9343,7 @@
       <c r="F191" s="65"/>
       <c r="G191" s="68"/>
     </row>
-    <row r="192" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="16"/>
       <c r="B192" s="19" t="s">
         <v>90</v>
@@ -9354,7 +9354,7 @@
       <c r="F192" s="66"/>
       <c r="G192" s="69"/>
     </row>
-    <row r="193" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="16">
         <v>3</v>
       </c>
@@ -9375,7 +9375,7 @@
       <c r="F193" s="64"/>
       <c r="G193" s="67"/>
     </row>
-    <row r="194" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="16"/>
       <c r="B194" s="18" t="s">
         <v>87</v>
@@ -9386,7 +9386,7 @@
       <c r="F194" s="65"/>
       <c r="G194" s="68"/>
     </row>
-    <row r="195" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A195" s="16"/>
       <c r="B195" s="19" t="s">
         <v>139</v>
@@ -9405,7 +9405,7 @@
       <c r="F195" s="65"/>
       <c r="G195" s="68"/>
     </row>
-    <row r="196" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="16"/>
       <c r="B196" s="18" t="s">
         <v>88</v>
@@ -9416,7 +9416,7 @@
       <c r="F196" s="65"/>
       <c r="G196" s="68"/>
     </row>
-    <row r="197" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A197" s="16"/>
       <c r="B197" s="19" t="s">
         <v>113</v>
@@ -9427,7 +9427,7 @@
       <c r="F197" s="65"/>
       <c r="G197" s="68"/>
     </row>
-    <row r="198" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="16"/>
       <c r="B198" s="19" t="s">
         <v>144</v>
@@ -9438,7 +9438,7 @@
       <c r="F198" s="65"/>
       <c r="G198" s="68"/>
     </row>
-    <row r="199" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="16"/>
       <c r="B199" s="17" t="s">
         <v>90</v>
@@ -9449,7 +9449,7 @@
       <c r="F199" s="65"/>
       <c r="G199" s="68"/>
     </row>
-    <row r="200" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="16"/>
       <c r="B200" s="17" t="s">
         <v>134</v>
@@ -9460,7 +9460,7 @@
       <c r="F200" s="66"/>
       <c r="G200" s="69"/>
     </row>
-    <row r="201" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="16">
         <v>4</v>
       </c>
@@ -9476,14 +9476,14 @@
       </c>
       <c r="E201" s="3">
         <f>D201*'Исходные данные'!$D$2</f>
-        <v>8.5015500000000001E-4</v>
+        <v>2.8338499999999998E-4</v>
       </c>
       <c r="F201" s="64"/>
       <c r="G201" s="67" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="16"/>
       <c r="B202" s="18" t="s">
         <v>87</v>
@@ -9494,7 +9494,7 @@
       <c r="F202" s="65"/>
       <c r="G202" s="68"/>
     </row>
-    <row r="203" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A203" s="16"/>
       <c r="B203" s="2" t="s">
         <v>25</v>
@@ -9508,12 +9508,12 @@
       </c>
       <c r="E203" s="3">
         <f>D203*'Исходные данные'!$D$2</f>
-        <v>8.5015499999999995E-7</v>
+        <v>2.8338499999999997E-7</v>
       </c>
       <c r="F203" s="65"/>
       <c r="G203" s="68"/>
     </row>
-    <row r="204" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="16"/>
       <c r="B204" s="18" t="s">
         <v>88</v>
@@ -9524,7 +9524,7 @@
       <c r="F204" s="65"/>
       <c r="G204" s="68"/>
     </row>
-    <row r="205" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A205" s="16"/>
       <c r="B205" s="19" t="s">
         <v>113</v>
@@ -9535,7 +9535,7 @@
       <c r="F205" s="65"/>
       <c r="G205" s="68"/>
     </row>
-    <row r="206" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="16"/>
       <c r="B206" s="17" t="s">
         <v>90</v>
@@ -9546,7 +9546,7 @@
       <c r="F206" s="65"/>
       <c r="G206" s="68"/>
     </row>
-    <row r="207" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="16"/>
       <c r="B207" s="17" t="s">
         <v>134</v>
@@ -9557,7 +9557,7 @@
       <c r="F207" s="66"/>
       <c r="G207" s="69"/>
     </row>
-    <row r="208" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="52" t="s">
         <v>80</v>
       </c>
@@ -9568,7 +9568,7 @@
       <c r="F208" s="53"/>
       <c r="G208" s="54"/>
     </row>
-    <row r="209" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="16">
         <v>1</v>
       </c>
@@ -9581,11 +9581,11 @@
       </c>
       <c r="D209" s="3">
         <f>D7</f>
-        <v>1.6485000000000002E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="E209" s="3">
         <f>D209*'Исходные данные'!$D$2</f>
-        <v>4.9455000000000007E-5</v>
+        <v>1.3611900000000003E-5</v>
       </c>
       <c r="F209" s="64" t="s">
         <v>33</v>
@@ -9594,7 +9594,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="16"/>
       <c r="B210" s="18" t="s">
         <v>87</v>
@@ -9605,7 +9605,7 @@
       <c r="F210" s="65"/>
       <c r="G210" s="68"/>
     </row>
-    <row r="211" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A211" s="16"/>
       <c r="B211" s="19" t="str">
         <f>B9</f>
@@ -9617,16 +9617,16 @@
       </c>
       <c r="D211" s="3">
         <f>D9</f>
-        <v>1.4836500000000002E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="E211" s="3">
         <f>D211*'Исходные данные'!$D$2</f>
-        <v>4.4509500000000006E-7</v>
+        <v>1.2250710000000002E-7</v>
       </c>
       <c r="F211" s="65"/>
       <c r="G211" s="68"/>
     </row>
-    <row r="212" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A212" s="16"/>
       <c r="B212" s="19" t="str">
         <f t="shared" ref="B212:D213" si="0">B10</f>
@@ -9638,16 +9638,16 @@
       </c>
       <c r="D212" s="3">
         <f t="shared" si="0"/>
-        <v>5.769750000000001E-7</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="E212" s="3">
         <f>D212*'Исходные данные'!$D$2</f>
-        <v>1.7309250000000003E-6</v>
+        <v>4.7641650000000014E-7</v>
       </c>
       <c r="F212" s="65"/>
       <c r="G212" s="68"/>
     </row>
-    <row r="213" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="16"/>
       <c r="B213" s="19" t="str">
         <f t="shared" si="0"/>
@@ -9659,16 +9659,16 @@
       </c>
       <c r="D213" s="3">
         <f t="shared" si="0"/>
-        <v>5.6049000000000005E-5</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="E213" s="3">
         <f>D213*'Исходные данные'!$D$2</f>
-        <v>1.68147E-4</v>
+        <v>4.6280460000000009E-5</v>
       </c>
       <c r="F213" s="65"/>
       <c r="G213" s="68"/>
     </row>
-    <row r="214" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="16"/>
       <c r="B214" s="18" t="s">
         <v>88</v>
@@ -9679,7 +9679,7 @@
       <c r="F214" s="65"/>
       <c r="G214" s="68"/>
     </row>
-    <row r="215" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="16"/>
       <c r="B215" s="17" t="s">
         <v>90</v>
@@ -9690,7 +9690,7 @@
       <c r="F215" s="66"/>
       <c r="G215" s="69"/>
     </row>
-    <row r="216" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="52" t="s">
         <v>81</v>
       </c>
@@ -9701,7 +9701,7 @@
       <c r="F216" s="53"/>
       <c r="G216" s="54"/>
     </row>
-    <row r="217" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A217" s="16">
         <v>1</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="16"/>
       <c r="B218" s="18" t="s">
         <v>87</v>
@@ -9732,7 +9732,7 @@
       <c r="F218" s="65"/>
       <c r="G218" s="68"/>
     </row>
-    <row r="219" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="16"/>
       <c r="B219" s="19" t="s">
         <v>16</v>
@@ -9748,7 +9748,7 @@
       <c r="F219" s="65"/>
       <c r="G219" s="68"/>
     </row>
-    <row r="220" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="16"/>
       <c r="B220" s="19" t="s">
         <v>150</v>
@@ -9764,7 +9764,7 @@
       <c r="F220" s="65"/>
       <c r="G220" s="68"/>
     </row>
-    <row r="221" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="16"/>
       <c r="B221" s="18" t="s">
         <v>88</v>
@@ -9775,7 +9775,7 @@
       <c r="F221" s="65"/>
       <c r="G221" s="68"/>
     </row>
-    <row r="222" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A222" s="16"/>
       <c r="B222" s="19" t="s">
         <v>152</v>
@@ -9786,7 +9786,7 @@
       <c r="F222" s="65"/>
       <c r="G222" s="68"/>
     </row>
-    <row r="223" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A223" s="16"/>
       <c r="B223" s="19" t="s">
         <v>115</v>
@@ -9797,7 +9797,7 @@
       <c r="F223" s="65"/>
       <c r="G223" s="68"/>
     </row>
-    <row r="224" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="16"/>
       <c r="B224" s="19" t="s">
         <v>153</v>
@@ -9808,7 +9808,7 @@
       <c r="F224" s="66"/>
       <c r="G224" s="69"/>
     </row>
-    <row r="225" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A225" s="16">
         <v>2</v>
       </c>
@@ -9828,7 +9828,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="16"/>
       <c r="B226" s="18" t="s">
         <v>87</v>
@@ -9839,7 +9839,7 @@
       <c r="F226" s="65"/>
       <c r="G226" s="68"/>
     </row>
-    <row r="227" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="16"/>
       <c r="B227" s="19" t="s">
         <v>16</v>
@@ -9855,7 +9855,7 @@
       <c r="F227" s="65"/>
       <c r="G227" s="68"/>
     </row>
-    <row r="228" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="16"/>
       <c r="B228" s="19" t="s">
         <v>150</v>
@@ -9871,7 +9871,7 @@
       <c r="F228" s="65"/>
       <c r="G228" s="68"/>
     </row>
-    <row r="229" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="16"/>
       <c r="B229" s="18" t="s">
         <v>88</v>
@@ -9882,7 +9882,7 @@
       <c r="F229" s="65"/>
       <c r="G229" s="68"/>
     </row>
-    <row r="230" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A230" s="16"/>
       <c r="B230" s="19" t="s">
         <v>155</v>
@@ -9893,7 +9893,7 @@
       <c r="F230" s="65"/>
       <c r="G230" s="68"/>
     </row>
-    <row r="231" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A231" s="16"/>
       <c r="B231" s="19" t="s">
         <v>156</v>
@@ -9904,7 +9904,7 @@
       <c r="F231" s="65"/>
       <c r="G231" s="68"/>
     </row>
-    <row r="232" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="16"/>
       <c r="B232" s="19" t="s">
         <v>157</v>
@@ -9915,7 +9915,7 @@
       <c r="F232" s="66"/>
       <c r="G232" s="69"/>
     </row>
-    <row r="233" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="22">
         <v>3</v>
       </c>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="D233" s="77">
         <f>('Исходные данные'!D19+'Исходные данные'!D2)/100</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E233" s="78"/>
       <c r="F233" s="25"/>
@@ -9935,7 +9935,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="27"/>
       <c r="B234" s="28"/>
       <c r="C234" s="27"/>
@@ -9944,7 +9944,7 @@
       <c r="F234" s="28"/>
       <c r="G234" s="27"/>
     </row>
-    <row r="235" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="21"/>
       <c r="B235" s="21"/>
       <c r="C235" s="79" t="s">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="G235" s="27"/>
     </row>
-    <row r="236" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="21"/>
       <c r="B236" s="21"/>
       <c r="C236" s="21"/>
@@ -9966,7 +9966,7 @@
       <c r="F236" s="21"/>
       <c r="G236" s="27"/>
     </row>
-    <row r="237" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="21"/>
       <c r="B237" s="21"/>
       <c r="C237" s="79" t="s">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="G237" s="27"/>
     </row>
-    <row r="238" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="21"/>
       <c r="B238" s="21"/>
       <c r="C238" s="21"/>
@@ -9988,7 +9988,7 @@
       <c r="F238" s="33"/>
       <c r="G238" s="27"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="34"/>
       <c r="B239" s="34"/>
       <c r="C239" s="34"/>
@@ -9996,7 +9996,7 @@
       <c r="E239" s="34"/>
       <c r="F239" s="35"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="36" t="s">
         <v>169</v>
       </c>
@@ -10007,7 +10007,7 @@
       <c r="F240" s="36"/>
       <c r="G240" s="36"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="36"/>
       <c r="B241" s="36"/>
       <c r="C241" s="36"/>
@@ -10016,7 +10016,7 @@
       <c r="F241" s="36"/>
       <c r="G241" s="36"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="36"/>
       <c r="B242" s="36"/>
       <c r="C242" s="36"/>
@@ -10025,7 +10025,7 @@
       <c r="F242" s="36"/>
       <c r="G242" s="36"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="36"/>
       <c r="B243" s="36"/>
       <c r="C243" s="36"/>
@@ -10034,7 +10034,7 @@
       <c r="F243" s="36"/>
       <c r="G243" s="36"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="36"/>
       <c r="B244" s="36"/>
       <c r="C244" s="36"/>
@@ -10043,7 +10043,7 @@
       <c r="F244" s="36"/>
       <c r="G244" s="36"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="36"/>
       <c r="B245" s="36"/>
       <c r="C245" s="36"/>
@@ -10052,7 +10052,7 @@
       <c r="F245" s="36"/>
       <c r="G245" s="36"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="36"/>
       <c r="B246" s="36"/>
       <c r="C246" s="36"/>
@@ -10061,7 +10061,7 @@
       <c r="F246" s="36"/>
       <c r="G246" s="36"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="36"/>
       <c r="B247" s="36"/>
       <c r="C247" s="36"/>
@@ -10070,7 +10070,7 @@
       <c r="F247" s="36"/>
       <c r="G247" s="36"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="34"/>
       <c r="B248" s="34"/>
       <c r="C248" s="34"/>
@@ -10078,7 +10078,7 @@
       <c r="E248" s="34"/>
       <c r="F248" s="35"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="34"/>
       <c r="B249" s="34"/>
       <c r="C249" s="34"/>
@@ -10086,7 +10086,7 @@
       <c r="E249" s="34"/>
       <c r="F249" s="35"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="34"/>
       <c r="B250" s="34"/>
       <c r="C250" s="34"/>
@@ -10094,7 +10094,7 @@
       <c r="E250" s="34"/>
       <c r="F250" s="35"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="34"/>
       <c r="B251" s="34"/>
       <c r="C251" s="34"/>
@@ -10102,7 +10102,7 @@
       <c r="E251" s="34"/>
       <c r="F251" s="35"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="34"/>
       <c r="B252" s="34"/>
       <c r="C252" s="34"/>
@@ -10110,7 +10110,7 @@
       <c r="E252" s="34"/>
       <c r="F252" s="35"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="34"/>
       <c r="B253" s="34"/>
       <c r="C253" s="34"/>
@@ -10118,7 +10118,7 @@
       <c r="E253" s="34"/>
       <c r="F253" s="35"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="34"/>
       <c r="B254" s="34"/>
       <c r="C254" s="34"/>
@@ -10126,7 +10126,7 @@
       <c r="E254" s="34"/>
       <c r="F254" s="35"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="34"/>
       <c r="B255" s="34"/>
       <c r="C255" s="34"/>
@@ -10134,7 +10134,7 @@
       <c r="E255" s="34"/>
       <c r="F255" s="35"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="34"/>
       <c r="B256" s="34"/>
       <c r="C256" s="34"/>
@@ -10142,7 +10142,7 @@
       <c r="E256" s="34"/>
       <c r="F256" s="35"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="34"/>
       <c r="B257" s="34"/>
       <c r="C257" s="34"/>
@@ -10150,7 +10150,7 @@
       <c r="E257" s="34"/>
       <c r="F257" s="35"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="34"/>
       <c r="B258" s="34"/>
       <c r="C258" s="34"/>
@@ -10158,7 +10158,7 @@
       <c r="E258" s="34"/>
       <c r="F258" s="35"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="34"/>
       <c r="B259" s="34"/>
       <c r="C259" s="34"/>
@@ -10166,7 +10166,7 @@
       <c r="E259" s="34"/>
       <c r="F259" s="35"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="34"/>
       <c r="B260" s="34"/>
       <c r="C260" s="34"/>
@@ -10174,7 +10174,7 @@
       <c r="E260" s="34"/>
       <c r="F260" s="35"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="34"/>
       <c r="B261" s="34"/>
       <c r="C261" s="34"/>
@@ -10182,7 +10182,7 @@
       <c r="E261" s="34"/>
       <c r="F261" s="35"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="34"/>
       <c r="B262" s="34"/>
       <c r="C262" s="34"/>
@@ -10190,7 +10190,7 @@
       <c r="E262" s="34"/>
       <c r="F262" s="35"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="34"/>
       <c r="B263" s="34"/>
       <c r="C263" s="34"/>
@@ -10198,7 +10198,7 @@
       <c r="E263" s="34"/>
       <c r="F263" s="35"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="34"/>
       <c r="B264" s="34"/>
       <c r="C264" s="34"/>
@@ -10206,7 +10206,7 @@
       <c r="E264" s="34"/>
       <c r="F264" s="35"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="34"/>
       <c r="B265" s="34"/>
       <c r="C265" s="34"/>
@@ -10214,7 +10214,7 @@
       <c r="E265" s="34"/>
       <c r="F265" s="35"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="34"/>
       <c r="B266" s="34"/>
       <c r="C266" s="34"/>
@@ -10222,7 +10222,7 @@
       <c r="E266" s="34"/>
       <c r="F266" s="35"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="34"/>
       <c r="B267" s="34"/>
       <c r="C267" s="34"/>
@@ -10230,7 +10230,7 @@
       <c r="E267" s="34"/>
       <c r="F267" s="35"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="34"/>
       <c r="B268" s="34"/>
       <c r="C268" s="34"/>
@@ -10238,7 +10238,7 @@
       <c r="E268" s="34"/>
       <c r="F268" s="35"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="34"/>
       <c r="B269" s="34"/>
       <c r="C269" s="34"/>
@@ -10246,7 +10246,7 @@
       <c r="E269" s="34"/>
       <c r="F269" s="35"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="34"/>
       <c r="B270" s="34"/>
       <c r="C270" s="34"/>
@@ -10254,7 +10254,7 @@
       <c r="E270" s="34"/>
       <c r="F270" s="35"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="34"/>
       <c r="B271" s="34"/>
       <c r="C271" s="34"/>
@@ -10262,7 +10262,7 @@
       <c r="E271" s="34"/>
       <c r="F271" s="35"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="34"/>
       <c r="B272" s="34"/>
       <c r="C272" s="34"/>
@@ -10270,7 +10270,7 @@
       <c r="E272" s="34"/>
       <c r="F272" s="35"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="34"/>
       <c r="B273" s="34"/>
       <c r="C273" s="34"/>
@@ -10278,7 +10278,7 @@
       <c r="E273" s="34"/>
       <c r="F273" s="35"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="34"/>
       <c r="B274" s="34"/>
       <c r="C274" s="34"/>
@@ -10286,7 +10286,7 @@
       <c r="E274" s="34"/>
       <c r="F274" s="35"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="34"/>
       <c r="B275" s="34"/>
       <c r="C275" s="34"/>
@@ -10294,7 +10294,7 @@
       <c r="E275" s="34"/>
       <c r="F275" s="35"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="34"/>
       <c r="B276" s="34"/>
       <c r="C276" s="34"/>
@@ -10302,7 +10302,7 @@
       <c r="E276" s="34"/>
       <c r="F276" s="35"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="34"/>
       <c r="B277" s="34"/>
       <c r="C277" s="34"/>
@@ -10310,7 +10310,7 @@
       <c r="E277" s="34"/>
       <c r="F277" s="35"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="34"/>
       <c r="B278" s="34"/>
       <c r="C278" s="34"/>
@@ -10318,7 +10318,7 @@
       <c r="E278" s="34"/>
       <c r="F278" s="35"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="34"/>
       <c r="B279" s="34"/>
       <c r="C279" s="34"/>
@@ -10326,7 +10326,7 @@
       <c r="E279" s="34"/>
       <c r="F279" s="35"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="34"/>
       <c r="B280" s="34"/>
       <c r="C280" s="34"/>
@@ -10334,7 +10334,7 @@
       <c r="E280" s="34"/>
       <c r="F280" s="35"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="34"/>
       <c r="B281" s="34"/>
       <c r="C281" s="34"/>
@@ -10342,7 +10342,7 @@
       <c r="E281" s="34"/>
       <c r="F281" s="35"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="34"/>
       <c r="B282" s="34"/>
       <c r="C282" s="34"/>
@@ -10350,7 +10350,7 @@
       <c r="E282" s="34"/>
       <c r="F282" s="35"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="34"/>
       <c r="B283" s="34"/>
       <c r="C283" s="34"/>
@@ -10358,7 +10358,7 @@
       <c r="E283" s="34"/>
       <c r="F283" s="35"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="34"/>
       <c r="B284" s="34"/>
       <c r="C284" s="34"/>
@@ -10366,7 +10366,7 @@
       <c r="E284" s="34"/>
       <c r="F284" s="35"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="34"/>
       <c r="B285" s="34"/>
       <c r="C285" s="34"/>
@@ -10374,7 +10374,7 @@
       <c r="E285" s="34"/>
       <c r="F285" s="35"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="34"/>
       <c r="B286" s="34"/>
       <c r="C286" s="34"/>
@@ -10382,7 +10382,7 @@
       <c r="E286" s="34"/>
       <c r="F286" s="35"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="34"/>
       <c r="B287" s="34"/>
       <c r="C287" s="34"/>
@@ -10390,7 +10390,7 @@
       <c r="E287" s="34"/>
       <c r="F287" s="35"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="34"/>
       <c r="B288" s="34"/>
       <c r="C288" s="34"/>
@@ -10398,7 +10398,7 @@
       <c r="E288" s="34"/>
       <c r="F288" s="35"/>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="34"/>
       <c r="B289" s="34"/>
       <c r="C289" s="34"/>
@@ -10406,7 +10406,7 @@
       <c r="E289" s="34"/>
       <c r="F289" s="35"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="34"/>
       <c r="B290" s="34"/>
       <c r="C290" s="34"/>
@@ -10414,7 +10414,7 @@
       <c r="E290" s="34"/>
       <c r="F290" s="35"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="34"/>
       <c r="B291" s="34"/>
       <c r="C291" s="34"/>
@@ -10422,7 +10422,7 @@
       <c r="E291" s="34"/>
       <c r="F291" s="35"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="34"/>
       <c r="B292" s="34"/>
       <c r="C292" s="34"/>
@@ -10430,7 +10430,7 @@
       <c r="E292" s="34"/>
       <c r="F292" s="35"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="34"/>
       <c r="B293" s="34"/>
       <c r="C293" s="34"/>
@@ -10438,7 +10438,7 @@
       <c r="E293" s="34"/>
       <c r="F293" s="35"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="34"/>
       <c r="B294" s="34"/>
       <c r="C294" s="34"/>
@@ -10446,7 +10446,7 @@
       <c r="E294" s="34"/>
       <c r="F294" s="35"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="34"/>
       <c r="B295" s="34"/>
       <c r="C295" s="34"/>
@@ -10454,7 +10454,7 @@
       <c r="E295" s="34"/>
       <c r="F295" s="35"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="34"/>
       <c r="B296" s="34"/>
       <c r="C296" s="34"/>
@@ -10462,7 +10462,7 @@
       <c r="E296" s="34"/>
       <c r="F296" s="35"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="34"/>
       <c r="B297" s="34"/>
       <c r="C297" s="34"/>
@@ -10470,7 +10470,7 @@
       <c r="E297" s="34"/>
       <c r="F297" s="35"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="34"/>
       <c r="B298" s="34"/>
       <c r="C298" s="34"/>
@@ -10478,7 +10478,7 @@
       <c r="E298" s="34"/>
       <c r="F298" s="35"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="34"/>
       <c r="B299" s="34"/>
       <c r="C299" s="34"/>
@@ -10486,7 +10486,7 @@
       <c r="E299" s="34"/>
       <c r="F299" s="35"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="34"/>
       <c r="B300" s="34"/>
       <c r="C300" s="34"/>
@@ -10494,7 +10494,7 @@
       <c r="E300" s="34"/>
       <c r="F300" s="35"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="34"/>
       <c r="B301" s="34"/>
       <c r="C301" s="34"/>
@@ -10502,7 +10502,7 @@
       <c r="E301" s="34"/>
       <c r="F301" s="35"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="34"/>
       <c r="B302" s="34"/>
       <c r="C302" s="34"/>
@@ -10510,7 +10510,7 @@
       <c r="E302" s="34"/>
       <c r="F302" s="35"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="34"/>
       <c r="B303" s="34"/>
       <c r="C303" s="34"/>
@@ -10518,7 +10518,7 @@
       <c r="E303" s="34"/>
       <c r="F303" s="35"/>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="34"/>
       <c r="B304" s="34"/>
       <c r="C304" s="34"/>
@@ -10526,7 +10526,7 @@
       <c r="E304" s="34"/>
       <c r="F304" s="35"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="34"/>
       <c r="B305" s="34"/>
       <c r="C305" s="34"/>
@@ -10534,7 +10534,7 @@
       <c r="E305" s="34"/>
       <c r="F305" s="35"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="34"/>
       <c r="B306" s="34"/>
       <c r="C306" s="34"/>
@@ -10542,7 +10542,7 @@
       <c r="E306" s="34"/>
       <c r="F306" s="35"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="34"/>
       <c r="B307" s="34"/>
       <c r="C307" s="34"/>
@@ -10550,7 +10550,7 @@
       <c r="E307" s="34"/>
       <c r="F307" s="35"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="34"/>
       <c r="B308" s="34"/>
       <c r="C308" s="34"/>
@@ -10558,7 +10558,7 @@
       <c r="E308" s="34"/>
       <c r="F308" s="35"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="34"/>
       <c r="B309" s="34"/>
       <c r="C309" s="34"/>
@@ -10566,7 +10566,7 @@
       <c r="E309" s="34"/>
       <c r="F309" s="35"/>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="34"/>
       <c r="B310" s="34"/>
       <c r="C310" s="34"/>
@@ -10574,7 +10574,7 @@
       <c r="E310" s="34"/>
       <c r="F310" s="35"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="34"/>
       <c r="B311" s="34"/>
       <c r="C311" s="34"/>
@@ -10582,7 +10582,7 @@
       <c r="E311" s="34"/>
       <c r="F311" s="35"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="34"/>
       <c r="B312" s="34"/>
       <c r="C312" s="34"/>
@@ -10590,7 +10590,7 @@
       <c r="E312" s="34"/>
       <c r="F312" s="35"/>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="34"/>
       <c r="B313" s="34"/>
       <c r="C313" s="34"/>
@@ -10598,7 +10598,7 @@
       <c r="E313" s="34"/>
       <c r="F313" s="35"/>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="34"/>
       <c r="B314" s="34"/>
       <c r="C314" s="34"/>
@@ -10606,7 +10606,7 @@
       <c r="E314" s="34"/>
       <c r="F314" s="35"/>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="34"/>
       <c r="B315" s="34"/>
       <c r="C315" s="34"/>
@@ -10614,7 +10614,7 @@
       <c r="E315" s="34"/>
       <c r="F315" s="35"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="34"/>
       <c r="B316" s="34"/>
       <c r="C316" s="34"/>
@@ -10622,7 +10622,7 @@
       <c r="E316" s="34"/>
       <c r="F316" s="35"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="34"/>
       <c r="B317" s="34"/>
       <c r="C317" s="34"/>
@@ -10630,7 +10630,7 @@
       <c r="E317" s="34"/>
       <c r="F317" s="35"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="34"/>
       <c r="B318" s="34"/>
       <c r="C318" s="34"/>
@@ -10638,7 +10638,7 @@
       <c r="E318" s="34"/>
       <c r="F318" s="35"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="34"/>
       <c r="B319" s="34"/>
       <c r="C319" s="34"/>
@@ -10646,7 +10646,7 @@
       <c r="E319" s="34"/>
       <c r="F319" s="35"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="34"/>
       <c r="B320" s="34"/>
       <c r="C320" s="34"/>
@@ -10654,7 +10654,7 @@
       <c r="E320" s="34"/>
       <c r="F320" s="35"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="34"/>
       <c r="B321" s="34"/>
       <c r="C321" s="34"/>
@@ -10662,7 +10662,7 @@
       <c r="E321" s="34"/>
       <c r="F321" s="35"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="34"/>
       <c r="B322" s="34"/>
       <c r="C322" s="34"/>
@@ -10670,7 +10670,7 @@
       <c r="E322" s="34"/>
       <c r="F322" s="35"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="34"/>
       <c r="B323" s="34"/>
       <c r="C323" s="34"/>
@@ -10678,7 +10678,7 @@
       <c r="E323" s="34"/>
       <c r="F323" s="35"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="34"/>
       <c r="B324" s="34"/>
       <c r="C324" s="34"/>
@@ -10686,7 +10686,7 @@
       <c r="E324" s="34"/>
       <c r="F324" s="35"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="34"/>
       <c r="B325" s="34"/>
       <c r="C325" s="34"/>
@@ -10694,7 +10694,7 @@
       <c r="E325" s="34"/>
       <c r="F325" s="35"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="34"/>
       <c r="B326" s="34"/>
       <c r="C326" s="34"/>
@@ -10702,7 +10702,7 @@
       <c r="E326" s="34"/>
       <c r="F326" s="35"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="34"/>
       <c r="B327" s="34"/>
       <c r="C327" s="34"/>
@@ -10710,7 +10710,7 @@
       <c r="E327" s="34"/>
       <c r="F327" s="35"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="34"/>
       <c r="B328" s="34"/>
       <c r="C328" s="34"/>
@@ -10718,7 +10718,7 @@
       <c r="E328" s="34"/>
       <c r="F328" s="35"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="34"/>
       <c r="B329" s="34"/>
       <c r="C329" s="34"/>
@@ -10726,7 +10726,7 @@
       <c r="E329" s="34"/>
       <c r="F329" s="35"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="34"/>
       <c r="B330" s="34"/>
       <c r="C330" s="34"/>
@@ -10734,7 +10734,7 @@
       <c r="E330" s="34"/>
       <c r="F330" s="35"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="34"/>
       <c r="B331" s="34"/>
       <c r="C331" s="34"/>
@@ -10742,7 +10742,7 @@
       <c r="E331" s="34"/>
       <c r="F331" s="35"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="34"/>
       <c r="B332" s="34"/>
       <c r="C332" s="34"/>
@@ -10750,7 +10750,7 @@
       <c r="E332" s="34"/>
       <c r="F332" s="35"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="34"/>
       <c r="B333" s="34"/>
       <c r="C333" s="34"/>
@@ -10758,7 +10758,7 @@
       <c r="E333" s="34"/>
       <c r="F333" s="35"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="34"/>
       <c r="B334" s="34"/>
       <c r="C334" s="34"/>
@@ -10766,7 +10766,7 @@
       <c r="E334" s="34"/>
       <c r="F334" s="35"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="34"/>
       <c r="B335" s="34"/>
       <c r="C335" s="34"/>
@@ -10774,7 +10774,7 @@
       <c r="E335" s="34"/>
       <c r="F335" s="35"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="34"/>
       <c r="B336" s="34"/>
       <c r="C336" s="34"/>
@@ -10782,7 +10782,7 @@
       <c r="E336" s="34"/>
       <c r="F336" s="35"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="37"/>
       <c r="B337" s="37"/>
       <c r="C337" s="37"/>
@@ -10790,7 +10790,7 @@
       <c r="E337" s="37"/>
       <c r="F337" s="38"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="37"/>
       <c r="B338" s="37"/>
       <c r="C338" s="37"/>
@@ -10798,7 +10798,7 @@
       <c r="E338" s="37"/>
       <c r="F338" s="38"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="37"/>
       <c r="B339" s="37"/>
       <c r="C339" s="37"/>
@@ -10806,7 +10806,7 @@
       <c r="E339" s="37"/>
       <c r="F339" s="38"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="37"/>
       <c r="B340" s="37"/>
       <c r="C340" s="37"/>
@@ -10814,7 +10814,7 @@
       <c r="E340" s="37"/>
       <c r="F340" s="38"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="37"/>
       <c r="B341" s="37"/>
       <c r="C341" s="37"/>
@@ -10822,7 +10822,7 @@
       <c r="E341" s="37"/>
       <c r="F341" s="38"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="37"/>
       <c r="B342" s="37"/>
       <c r="C342" s="37"/>
@@ -10830,7 +10830,7 @@
       <c r="E342" s="37"/>
       <c r="F342" s="38"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="37"/>
       <c r="B343" s="37"/>
       <c r="C343" s="37"/>
@@ -10838,7 +10838,7 @@
       <c r="E343" s="37"/>
       <c r="F343" s="38"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="37"/>
       <c r="B344" s="37"/>
       <c r="C344" s="37"/>
@@ -10846,7 +10846,7 @@
       <c r="E344" s="37"/>
       <c r="F344" s="38"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="37"/>
       <c r="B345" s="37"/>
       <c r="C345" s="37"/>
@@ -10854,7 +10854,7 @@
       <c r="E345" s="37"/>
       <c r="F345" s="38"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="37"/>
       <c r="B346" s="37"/>
       <c r="C346" s="37"/>
@@ -10862,7 +10862,7 @@
       <c r="E346" s="37"/>
       <c r="F346" s="38"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="37"/>
       <c r="B347" s="37"/>
       <c r="C347" s="37"/>
@@ -10870,7 +10870,7 @@
       <c r="E347" s="37"/>
       <c r="F347" s="38"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="37"/>
       <c r="B348" s="37"/>
       <c r="C348" s="37"/>
@@ -10878,7 +10878,7 @@
       <c r="E348" s="37"/>
       <c r="F348" s="38"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="37"/>
       <c r="B349" s="37"/>
       <c r="C349" s="37"/>
@@ -10886,7 +10886,7 @@
       <c r="E349" s="37"/>
       <c r="F349" s="38"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="37"/>
       <c r="B350" s="37"/>
       <c r="C350" s="37"/>
@@ -10894,7 +10894,7 @@
       <c r="E350" s="37"/>
       <c r="F350" s="38"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="37"/>
       <c r="B351" s="37"/>
       <c r="C351" s="37"/>
@@ -10902,7 +10902,7 @@
       <c r="E351" s="37"/>
       <c r="F351" s="38"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="37"/>
       <c r="B352" s="37"/>
       <c r="C352" s="37"/>
@@ -10910,7 +10910,7 @@
       <c r="E352" s="37"/>
       <c r="F352" s="38"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="37"/>
       <c r="B353" s="37"/>
       <c r="C353" s="37"/>
@@ -10918,7 +10918,7 @@
       <c r="E353" s="37"/>
       <c r="F353" s="38"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="37"/>
       <c r="B354" s="37"/>
       <c r="C354" s="37"/>
@@ -10926,7 +10926,7 @@
       <c r="E354" s="37"/>
       <c r="F354" s="38"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="37"/>
       <c r="B355" s="37"/>
       <c r="C355" s="37"/>
@@ -10934,7 +10934,7 @@
       <c r="E355" s="37"/>
       <c r="F355" s="38"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="37"/>
       <c r="B356" s="37"/>
       <c r="C356" s="37"/>
@@ -10942,7 +10942,7 @@
       <c r="E356" s="37"/>
       <c r="F356" s="38"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="37"/>
       <c r="B357" s="37"/>
       <c r="C357" s="37"/>
@@ -10950,7 +10950,7 @@
       <c r="E357" s="37"/>
       <c r="F357" s="38"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="37"/>
       <c r="B358" s="37"/>
       <c r="C358" s="37"/>
@@ -10958,7 +10958,7 @@
       <c r="E358" s="37"/>
       <c r="F358" s="38"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="37"/>
       <c r="B359" s="37"/>
       <c r="C359" s="37"/>
@@ -10966,7 +10966,7 @@
       <c r="E359" s="37"/>
       <c r="F359" s="38"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="37"/>
       <c r="B360" s="37"/>
       <c r="C360" s="37"/>
@@ -10974,7 +10974,7 @@
       <c r="E360" s="37"/>
       <c r="F360" s="38"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="37"/>
       <c r="B361" s="37"/>
       <c r="C361" s="37"/>
@@ -10982,7 +10982,7 @@
       <c r="E361" s="37"/>
       <c r="F361" s="38"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" s="37"/>
       <c r="B362" s="37"/>
       <c r="C362" s="37"/>
@@ -10990,7 +10990,7 @@
       <c r="E362" s="37"/>
       <c r="F362" s="38"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="37"/>
       <c r="B363" s="37"/>
       <c r="C363" s="37"/>
@@ -10998,7 +10998,7 @@
       <c r="E363" s="37"/>
       <c r="F363" s="38"/>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="37"/>
       <c r="B364" s="37"/>
       <c r="C364" s="37"/>
@@ -11006,7 +11006,7 @@
       <c r="E364" s="37"/>
       <c r="F364" s="38"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="37"/>
       <c r="B365" s="37"/>
       <c r="C365" s="37"/>
@@ -11014,7 +11014,7 @@
       <c r="E365" s="37"/>
       <c r="F365" s="38"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="37"/>
       <c r="B366" s="37"/>
       <c r="C366" s="37"/>
@@ -11022,7 +11022,7 @@
       <c r="E366" s="37"/>
       <c r="F366" s="38"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="37"/>
       <c r="B367" s="37"/>
       <c r="C367" s="37"/>
@@ -11030,7 +11030,7 @@
       <c r="E367" s="37"/>
       <c r="F367" s="38"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="37"/>
       <c r="B368" s="37"/>
       <c r="C368" s="37"/>
@@ -11038,7 +11038,7 @@
       <c r="E368" s="37"/>
       <c r="F368" s="38"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="37"/>
       <c r="B369" s="37"/>
       <c r="C369" s="37"/>
@@ -11046,7 +11046,7 @@
       <c r="E369" s="37"/>
       <c r="F369" s="38"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="37"/>
       <c r="B370" s="37"/>
       <c r="C370" s="37"/>
@@ -11054,7 +11054,7 @@
       <c r="E370" s="37"/>
       <c r="F370" s="38"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="37"/>
       <c r="B371" s="37"/>
       <c r="C371" s="37"/>
@@ -11062,7 +11062,7 @@
       <c r="E371" s="37"/>
       <c r="F371" s="38"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="37"/>
       <c r="B372" s="37"/>
       <c r="C372" s="37"/>
@@ -11070,7 +11070,7 @@
       <c r="E372" s="37"/>
       <c r="F372" s="38"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="37"/>
       <c r="B373" s="37"/>
       <c r="C373" s="37"/>
@@ -11078,7 +11078,7 @@
       <c r="E373" s="37"/>
       <c r="F373" s="38"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="37"/>
       <c r="B374" s="37"/>
       <c r="C374" s="37"/>
@@ -11086,7 +11086,7 @@
       <c r="E374" s="37"/>
       <c r="F374" s="38"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="37"/>
       <c r="B375" s="37"/>
       <c r="C375" s="37"/>
@@ -11094,7 +11094,7 @@
       <c r="E375" s="37"/>
       <c r="F375" s="38"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="37"/>
       <c r="B376" s="37"/>
       <c r="C376" s="37"/>
@@ -11102,7 +11102,7 @@
       <c r="E376" s="37"/>
       <c r="F376" s="38"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="37"/>
       <c r="B377" s="37"/>
       <c r="C377" s="37"/>
@@ -11110,7 +11110,7 @@
       <c r="E377" s="37"/>
       <c r="F377" s="38"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="37"/>
       <c r="B378" s="37"/>
       <c r="C378" s="37"/>
@@ -11118,7 +11118,7 @@
       <c r="E378" s="37"/>
       <c r="F378" s="38"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="37"/>
       <c r="B379" s="37"/>
       <c r="C379" s="37"/>
@@ -11126,7 +11126,7 @@
       <c r="E379" s="37"/>
       <c r="F379" s="38"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="37"/>
       <c r="B380" s="37"/>
       <c r="C380" s="37"/>
@@ -11134,7 +11134,7 @@
       <c r="E380" s="37"/>
       <c r="F380" s="38"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="37"/>
       <c r="B381" s="37"/>
       <c r="C381" s="37"/>
@@ -11142,7 +11142,7 @@
       <c r="E381" s="37"/>
       <c r="F381" s="38"/>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="37"/>
       <c r="B382" s="37"/>
       <c r="C382" s="37"/>
@@ -11150,7 +11150,7 @@
       <c r="E382" s="37"/>
       <c r="F382" s="38"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="37"/>
       <c r="B383" s="37"/>
       <c r="C383" s="37"/>
@@ -11158,7 +11158,7 @@
       <c r="E383" s="37"/>
       <c r="F383" s="38"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="37"/>
       <c r="B384" s="37"/>
       <c r="C384" s="37"/>
@@ -11166,7 +11166,7 @@
       <c r="E384" s="37"/>
       <c r="F384" s="38"/>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="37"/>
       <c r="B385" s="37"/>
       <c r="C385" s="37"/>
@@ -11174,7 +11174,7 @@
       <c r="E385" s="37"/>
       <c r="F385" s="38"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="37"/>
       <c r="B386" s="37"/>
       <c r="C386" s="37"/>
@@ -11182,7 +11182,7 @@
       <c r="E386" s="37"/>
       <c r="F386" s="38"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="37"/>
       <c r="B387" s="37"/>
       <c r="C387" s="37"/>
@@ -11190,7 +11190,7 @@
       <c r="E387" s="37"/>
       <c r="F387" s="38"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="37"/>
       <c r="B388" s="37"/>
       <c r="C388" s="37"/>
@@ -11198,7 +11198,7 @@
       <c r="E388" s="37"/>
       <c r="F388" s="38"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="37"/>
       <c r="B389" s="37"/>
       <c r="C389" s="37"/>
@@ -11206,7 +11206,7 @@
       <c r="E389" s="37"/>
       <c r="F389" s="38"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="37"/>
       <c r="B390" s="37"/>
       <c r="C390" s="37"/>
@@ -11214,7 +11214,7 @@
       <c r="E390" s="37"/>
       <c r="F390" s="38"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="37"/>
       <c r="B391" s="37"/>
       <c r="C391" s="37"/>
@@ -11222,7 +11222,7 @@
       <c r="E391" s="37"/>
       <c r="F391" s="38"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" s="37"/>
       <c r="B392" s="37"/>
       <c r="C392" s="37"/>
@@ -11230,7 +11230,7 @@
       <c r="E392" s="37"/>
       <c r="F392" s="38"/>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" s="37"/>
       <c r="B393" s="37"/>
       <c r="C393" s="37"/>
@@ -11238,7 +11238,7 @@
       <c r="E393" s="37"/>
       <c r="F393" s="38"/>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="37"/>
       <c r="B394" s="37"/>
       <c r="C394" s="37"/>
@@ -11246,7 +11246,7 @@
       <c r="E394" s="37"/>
       <c r="F394" s="38"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="37"/>
       <c r="B395" s="37"/>
       <c r="C395" s="37"/>
@@ -11254,7 +11254,7 @@
       <c r="E395" s="37"/>
       <c r="F395" s="38"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="37"/>
       <c r="B396" s="37"/>
       <c r="C396" s="37"/>
@@ -11262,7 +11262,7 @@
       <c r="E396" s="37"/>
       <c r="F396" s="38"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="37"/>
       <c r="B397" s="37"/>
       <c r="C397" s="37"/>
@@ -11270,7 +11270,7 @@
       <c r="E397" s="37"/>
       <c r="F397" s="38"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="37"/>
       <c r="B398" s="37"/>
       <c r="C398" s="37"/>
@@ -11278,7 +11278,7 @@
       <c r="E398" s="37"/>
       <c r="F398" s="38"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="37"/>
       <c r="B399" s="37"/>
       <c r="C399" s="37"/>
@@ -11286,7 +11286,7 @@
       <c r="E399" s="37"/>
       <c r="F399" s="38"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="37"/>
       <c r="B400" s="37"/>
       <c r="C400" s="37"/>
@@ -11294,7 +11294,7 @@
       <c r="E400" s="37"/>
       <c r="F400" s="38"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="37"/>
       <c r="B401" s="37"/>
       <c r="C401" s="37"/>
@@ -11302,7 +11302,7 @@
       <c r="E401" s="37"/>
       <c r="F401" s="38"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="37"/>
       <c r="B402" s="37"/>
       <c r="C402" s="37"/>
@@ -11310,7 +11310,7 @@
       <c r="E402" s="37"/>
       <c r="F402" s="38"/>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="37"/>
       <c r="B403" s="37"/>
       <c r="C403" s="37"/>
@@ -11318,7 +11318,7 @@
       <c r="E403" s="37"/>
       <c r="F403" s="38"/>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="37"/>
       <c r="B404" s="37"/>
       <c r="C404" s="37"/>
@@ -11326,7 +11326,7 @@
       <c r="E404" s="37"/>
       <c r="F404" s="38"/>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="37"/>
       <c r="B405" s="37"/>
       <c r="C405" s="37"/>
@@ -11334,7 +11334,7 @@
       <c r="E405" s="37"/>
       <c r="F405" s="38"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="37"/>
       <c r="B406" s="37"/>
       <c r="C406" s="37"/>
@@ -11342,7 +11342,7 @@
       <c r="E406" s="37"/>
       <c r="F406" s="38"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="37"/>
       <c r="B407" s="37"/>
       <c r="C407" s="37"/>
@@ -11350,7 +11350,7 @@
       <c r="E407" s="37"/>
       <c r="F407" s="38"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="37"/>
       <c r="B408" s="37"/>
       <c r="C408" s="37"/>
@@ -11358,7 +11358,7 @@
       <c r="E408" s="37"/>
       <c r="F408" s="38"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="37"/>
       <c r="B409" s="37"/>
       <c r="C409" s="37"/>
@@ -11366,7 +11366,7 @@
       <c r="E409" s="37"/>
       <c r="F409" s="38"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="37"/>
       <c r="B410" s="37"/>
       <c r="C410" s="37"/>
@@ -11374,7 +11374,7 @@
       <c r="E410" s="37"/>
       <c r="F410" s="38"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="37"/>
       <c r="B411" s="37"/>
       <c r="C411" s="37"/>
@@ -11382,7 +11382,7 @@
       <c r="E411" s="37"/>
       <c r="F411" s="38"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="37"/>
       <c r="B412" s="37"/>
       <c r="C412" s="37"/>
@@ -11390,7 +11390,7 @@
       <c r="E412" s="37"/>
       <c r="F412" s="38"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="37"/>
       <c r="B413" s="37"/>
       <c r="C413" s="37"/>
@@ -11398,7 +11398,7 @@
       <c r="E413" s="37"/>
       <c r="F413" s="38"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="37"/>
       <c r="B414" s="37"/>
       <c r="C414" s="37"/>
@@ -11406,7 +11406,7 @@
       <c r="E414" s="37"/>
       <c r="F414" s="38"/>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="37"/>
       <c r="B415" s="37"/>
       <c r="C415" s="37"/>
@@ -11414,7 +11414,7 @@
       <c r="E415" s="37"/>
       <c r="F415" s="38"/>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="37"/>
       <c r="B416" s="37"/>
       <c r="C416" s="37"/>
@@ -11422,7 +11422,7 @@
       <c r="E416" s="37"/>
       <c r="F416" s="38"/>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="37"/>
       <c r="B417" s="37"/>
       <c r="C417" s="37"/>
@@ -11430,7 +11430,7 @@
       <c r="E417" s="37"/>
       <c r="F417" s="38"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="37"/>
       <c r="B418" s="37"/>
       <c r="C418" s="37"/>
@@ -11438,7 +11438,7 @@
       <c r="E418" s="37"/>
       <c r="F418" s="38"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="37"/>
       <c r="B419" s="37"/>
       <c r="C419" s="37"/>
@@ -11446,7 +11446,7 @@
       <c r="E419" s="37"/>
       <c r="F419" s="38"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="37"/>
       <c r="B420" s="37"/>
       <c r="C420" s="37"/>
@@ -11454,7 +11454,7 @@
       <c r="E420" s="37"/>
       <c r="F420" s="38"/>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="37"/>
       <c r="B421" s="37"/>
       <c r="C421" s="37"/>
@@ -11462,7 +11462,7 @@
       <c r="E421" s="37"/>
       <c r="F421" s="38"/>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="37"/>
       <c r="B422" s="37"/>
       <c r="C422" s="37"/>
@@ -11470,7 +11470,7 @@
       <c r="E422" s="37"/>
       <c r="F422" s="38"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="37"/>
       <c r="B423" s="37"/>
       <c r="C423" s="37"/>
@@ -11478,7 +11478,7 @@
       <c r="E423" s="37"/>
       <c r="F423" s="38"/>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="37"/>
       <c r="B424" s="37"/>
       <c r="C424" s="37"/>
@@ -11486,7 +11486,7 @@
       <c r="E424" s="37"/>
       <c r="F424" s="38"/>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="37"/>
       <c r="B425" s="37"/>
       <c r="C425" s="37"/>
@@ -11494,7 +11494,7 @@
       <c r="E425" s="37"/>
       <c r="F425" s="38"/>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="37"/>
       <c r="B426" s="37"/>
       <c r="C426" s="37"/>
@@ -11502,7 +11502,7 @@
       <c r="E426" s="37"/>
       <c r="F426" s="38"/>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="37"/>
       <c r="B427" s="37"/>
       <c r="C427" s="37"/>
@@ -11510,7 +11510,7 @@
       <c r="E427" s="37"/>
       <c r="F427" s="38"/>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="37"/>
       <c r="B428" s="37"/>
       <c r="C428" s="37"/>
@@ -11518,7 +11518,7 @@
       <c r="E428" s="37"/>
       <c r="F428" s="38"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="37"/>
       <c r="B429" s="37"/>
       <c r="C429" s="37"/>
@@ -11526,7 +11526,7 @@
       <c r="E429" s="37"/>
       <c r="F429" s="38"/>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="37"/>
       <c r="B430" s="37"/>
       <c r="C430" s="37"/>
@@ -11534,7 +11534,7 @@
       <c r="E430" s="37"/>
       <c r="F430" s="38"/>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="37"/>
       <c r="B431" s="37"/>
       <c r="C431" s="37"/>
@@ -11542,7 +11542,7 @@
       <c r="E431" s="37"/>
       <c r="F431" s="38"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="37"/>
       <c r="B432" s="37"/>
       <c r="C432" s="37"/>
@@ -11550,7 +11550,7 @@
       <c r="E432" s="37"/>
       <c r="F432" s="38"/>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="37"/>
       <c r="B433" s="37"/>
       <c r="C433" s="37"/>
@@ -11558,7 +11558,7 @@
       <c r="E433" s="37"/>
       <c r="F433" s="38"/>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="37"/>
       <c r="B434" s="37"/>
       <c r="C434" s="37"/>
@@ -11566,7 +11566,7 @@
       <c r="E434" s="37"/>
       <c r="F434" s="38"/>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="37"/>
       <c r="B435" s="37"/>
       <c r="C435" s="37"/>
@@ -11574,7 +11574,7 @@
       <c r="E435" s="37"/>
       <c r="F435" s="38"/>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="37"/>
       <c r="B436" s="37"/>
       <c r="C436" s="37"/>
@@ -11582,7 +11582,7 @@
       <c r="E436" s="37"/>
       <c r="F436" s="38"/>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="37"/>
       <c r="B437" s="37"/>
       <c r="C437" s="37"/>
@@ -11590,7 +11590,7 @@
       <c r="E437" s="37"/>
       <c r="F437" s="38"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="37"/>
       <c r="B438" s="37"/>
       <c r="C438" s="37"/>
@@ -11598,7 +11598,7 @@
       <c r="E438" s="37"/>
       <c r="F438" s="38"/>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="37"/>
       <c r="B439" s="37"/>
       <c r="C439" s="37"/>
@@ -11606,7 +11606,7 @@
       <c r="E439" s="37"/>
       <c r="F439" s="38"/>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="37"/>
       <c r="B440" s="37"/>
       <c r="C440" s="37"/>
@@ -11614,7 +11614,7 @@
       <c r="E440" s="37"/>
       <c r="F440" s="38"/>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="37"/>
       <c r="B441" s="37"/>
       <c r="C441" s="37"/>
@@ -11622,7 +11622,7 @@
       <c r="E441" s="37"/>
       <c r="F441" s="38"/>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="37"/>
       <c r="B442" s="37"/>
       <c r="C442" s="37"/>
@@ -11630,7 +11630,7 @@
       <c r="E442" s="37"/>
       <c r="F442" s="38"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="37"/>
       <c r="B443" s="37"/>
       <c r="C443" s="37"/>
@@ -11638,7 +11638,7 @@
       <c r="E443" s="37"/>
       <c r="F443" s="38"/>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="37"/>
       <c r="B444" s="37"/>
       <c r="C444" s="37"/>
@@ -11646,7 +11646,7 @@
       <c r="E444" s="37"/>
       <c r="F444" s="38"/>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="37"/>
       <c r="B445" s="37"/>
       <c r="C445" s="37"/>
@@ -11654,7 +11654,7 @@
       <c r="E445" s="37"/>
       <c r="F445" s="38"/>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="37"/>
       <c r="B446" s="37"/>
       <c r="C446" s="37"/>
@@ -11662,7 +11662,7 @@
       <c r="E446" s="37"/>
       <c r="F446" s="38"/>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="37"/>
       <c r="B447" s="37"/>
       <c r="C447" s="37"/>
@@ -11670,7 +11670,7 @@
       <c r="E447" s="37"/>
       <c r="F447" s="38"/>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="39"/>
       <c r="B448" s="39"/>
       <c r="C448" s="39"/>
@@ -11678,7 +11678,7 @@
       <c r="E448" s="39"/>
       <c r="F448" s="40"/>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="39"/>
       <c r="B449" s="39"/>
       <c r="C449" s="39"/>
@@ -11686,7 +11686,7 @@
       <c r="E449" s="39"/>
       <c r="F449" s="40"/>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="39"/>
       <c r="B450" s="39"/>
       <c r="C450" s="39"/>
@@ -11694,7 +11694,7 @@
       <c r="E450" s="39"/>
       <c r="F450" s="40"/>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="39"/>
       <c r="B451" s="39"/>
       <c r="C451" s="39"/>
@@ -11702,7 +11702,7 @@
       <c r="E451" s="39"/>
       <c r="F451" s="40"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" s="39"/>
       <c r="B452" s="39"/>
       <c r="C452" s="39"/>
@@ -11710,7 +11710,7 @@
       <c r="E452" s="39"/>
       <c r="F452" s="40"/>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="39"/>
       <c r="B453" s="39"/>
       <c r="C453" s="39"/>
@@ -11718,7 +11718,7 @@
       <c r="E453" s="39"/>
       <c r="F453" s="40"/>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="39"/>
       <c r="B454" s="39"/>
       <c r="C454" s="39"/>
